--- a/P012-excavator-split_data_files/output/17_22_05_2017_template.xlsx
+++ b/P012-excavator-split_data_files/output/17_22_05_2017_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Excavator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MPDM 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excavator" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPDM 1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Excavator'!$A$1:$S$111</definedName>
@@ -1000,11 +1000,7 @@
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="48" t="n"/>
       <c r="J6" s="2" t="n"/>
-      <c r="L6" s="47" t="inlineStr">
-        <is>
-          <t>Date:</t>
-        </is>
-      </c>
+      <c r="L6" s="47" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
@@ -1163,13 +1159,17 @@
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I11" s="7" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J11" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K11" s="7" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n">
         <v>1</v>
@@ -1224,13 +1224,17 @@
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I12" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J12" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K12" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n">
         <v>1</v>
@@ -1273,13 +1277,17 @@
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I13" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J13" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K13" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n">
         <v>1</v>
@@ -1322,13 +1330,17 @@
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I14" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J14" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K14" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n">
         <v>1</v>
@@ -1371,13 +1383,17 @@
         </is>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I15" s="9" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J15" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K15" s="9" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n">
         <v>1</v>
@@ -1420,13 +1436,17 @@
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I16" s="7" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.86</v>
+      </c>
       <c r="J16" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K16" s="7" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n">
         <v>1</v>
@@ -1469,13 +1489,17 @@
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I17" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J17" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K17" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n">
         <v>1</v>
@@ -1518,13 +1542,17 @@
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I18" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J18" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K18" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n">
         <v>1</v>
@@ -1567,13 +1595,17 @@
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I19" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J19" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K19" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n">
         <v>1</v>
@@ -1616,13 +1648,17 @@
         </is>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I20" s="9" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J20" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K20" s="9" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n">
         <v>1</v>
@@ -1665,13 +1701,17 @@
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I21" s="7" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J21" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K21" s="7" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n">
         <v>1</v>
@@ -1714,13 +1754,17 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I22" s="8" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>0.98</v>
+      </c>
       <c r="J22" s="8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K22" s="8" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n">
         <v>1</v>
@@ -1738,23 +1782,49 @@
       <c r="S22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 13</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
+      <c r="B23" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8" t="n"/>
-      <c r="N23" s="8" t="n"/>
+      <c r="M23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O23" s="8">
         <f>3600*M23*H23*I23*K23/(J23*N23*60)</f>
         <v/>
@@ -1765,23 +1835,49 @@
       <c r="S23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 14</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
+      <c r="B24" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
+      <c r="M24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O24" s="8">
         <f>3600*M24*H24*I24*K24/(J24*N24*60)</f>
         <v/>
@@ -1792,23 +1888,49 @@
       <c r="S24" s="8" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 15</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
+      <c r="B25" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+      <c r="M25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O25" s="9">
         <f>3600*M25*H25*I25*K25/(J25*N25*60)</f>
         <v/>
@@ -1819,23 +1941,49 @@
       <c r="S25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 16</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="B26" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
+      <c r="M26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O26" s="7">
         <f>3600*M26*H26*I26*K26/(J26*N26*60)</f>
         <v/>
@@ -1846,23 +1994,49 @@
       <c r="S26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 17</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
+      <c r="B27" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
-      <c r="N27" s="8" t="n"/>
+      <c r="M27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O27" s="8">
         <f>3600*M27*H27*I27*K27/(J27*N27*60)</f>
         <v/>
@@ -1873,23 +2047,49 @@
       <c r="S27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 18</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
+      <c r="B28" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
-      <c r="N28" s="8" t="n"/>
+      <c r="M28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O28" s="8">
         <f>3600*M28*H28*I28*K28/(J28*N28*60)</f>
         <v/>
@@ -1900,23 +2100,49 @@
       <c r="S28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 19</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
+      <c r="B29" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="8" t="n"/>
+      <c r="M29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O29" s="8">
         <f>3600*M29*H29*I29*K29/(J29*N29*60)</f>
         <v/>
@@ -1927,23 +2153,49 @@
       <c r="S29" s="8" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 20</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
+      <c r="B30" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
+      <c r="M30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O30" s="9">
         <f>3600*M30*H30*I30*K30/(J30*N30*60)</f>
         <v/>
@@ -1954,23 +2206,49 @@
       <c r="S30" s="9" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 21</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
+      <c r="B31" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
+      <c r="M31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O31" s="7">
         <f>3600*M31*H31*I31*K31/(J31*N31*60)</f>
         <v/>
@@ -1981,23 +2259,49 @@
       <c r="S31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 22</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
+      <c r="B32" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
+      <c r="M32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O32" s="8">
         <f>3600*M32*H32*I32*K32/(J32*N32*60)</f>
         <v/>
@@ -2008,23 +2312,49 @@
       <c r="S32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 23</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
+      <c r="B33" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
+      <c r="M33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O33" s="8">
         <f>3600*M33*H33*I33*K33/(J33*N33*60)</f>
         <v/>
@@ -2035,23 +2365,49 @@
       <c r="S33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 24</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
+      <c r="B34" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="8" t="n"/>
+      <c r="M34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O34" s="8">
         <f>3600*M34*H34*I34*K34/(J34*N34*60)</f>
         <v/>
@@ -2062,23 +2418,49 @@
       <c r="S34" s="8" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 25</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
+      <c r="B35" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L35" s="9" t="n"/>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="9" t="n"/>
+      <c r="M35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O35" s="9">
         <f>3600*M35*H35*I35*K35/(J35*N35*60)</f>
         <v/>
@@ -2089,23 +2471,49 @@
       <c r="S35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 26</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
+      <c r="B36" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
+      <c r="M36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O36" s="7">
         <f>3600*M36*H36*I36*K36/(J36*N36*60)</f>
         <v/>
@@ -2116,23 +2524,49 @@
       <c r="S36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 27</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
+      <c r="B37" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
+      <c r="M37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O37" s="8">
         <f>3600*M37*H37*I37*K37/(J37*N37*60)</f>
         <v/>
@@ -2143,23 +2577,49 @@
       <c r="S37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 28</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
+      <c r="B38" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="8" t="n"/>
+      <c r="M38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O38" s="8">
         <f>3600*M38*H38*I38*K38/(J38*N38*60)</f>
         <v/>
@@ -2170,23 +2630,49 @@
       <c r="S38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 29</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
+      <c r="B39" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L39" s="8" t="n"/>
-      <c r="M39" s="8" t="n"/>
-      <c r="N39" s="8" t="n"/>
+      <c r="M39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O39" s="8">
         <f>3600*M39*H39*I39*K39/(J39*N39*60)</f>
         <v/>
@@ -2197,23 +2683,49 @@
       <c r="S39" s="8" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 30</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
+      <c r="B40" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
+      <c r="M40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O40" s="9">
         <f>3600*M40*H40*I40*K40/(J40*N40*60)</f>
         <v/>
@@ -2224,23 +2736,49 @@
       <c r="S40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 31</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
+      <c r="B41" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
-      <c r="N41" s="7" t="n"/>
+      <c r="M41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O41" s="7">
         <f>3600*M41*H41*I41*K41/(J41*N41*60)</f>
         <v/>
@@ -2251,23 +2789,49 @@
       <c r="S41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 32</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
+      <c r="B42" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L42" s="8" t="n"/>
-      <c r="M42" s="8" t="n"/>
-      <c r="N42" s="8" t="n"/>
+      <c r="M42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O42" s="8">
         <f>3600*M42*H42*I42*K42/(J42*N42*60)</f>
         <v/>
@@ -2278,23 +2842,49 @@
       <c r="S42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 33</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
+      <c r="B43" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L43" s="8" t="n"/>
-      <c r="M43" s="8" t="n"/>
-      <c r="N43" s="8" t="n"/>
+      <c r="M43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O43" s="8">
         <f>3600*M43*H43*I43*K43/(J43*N43*60)</f>
         <v/>
@@ -2305,23 +2895,49 @@
       <c r="S43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 34</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
+      <c r="B44" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L44" s="8" t="n"/>
-      <c r="M44" s="8" t="n"/>
-      <c r="N44" s="8" t="n"/>
+      <c r="M44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O44" s="8">
         <f>3600*M44*H44*I44*K44/(J44*N44*60)</f>
         <v/>
@@ -2332,23 +2948,49 @@
       <c r="S44" s="8" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 35</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
+      <c r="B45" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
-      <c r="N45" s="9" t="n"/>
+      <c r="M45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O45" s="9">
         <f>3600*M45*H45*I45*K45/(J45*N45*60)</f>
         <v/>
@@ -2359,23 +3001,49 @@
       <c r="S45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 36</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
+      <c r="B46" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="7" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
-      <c r="N46" s="7" t="n"/>
+      <c r="M46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O46" s="7">
         <f>3600*M46*H46*I46*K46/(J46*N46*60)</f>
         <v/>
@@ -2386,23 +3054,49 @@
       <c r="S46" s="7" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 37</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
+      <c r="B47" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="M47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O47" s="8">
         <f>3600*M47*H47*I47*K47/(J47*N47*60)</f>
         <v/>
@@ -2413,23 +3107,49 @@
       <c r="S47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 38</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
+      <c r="B48" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K48" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
+      <c r="M48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O48" s="8">
         <f>3600*M48*H48*I48*K48/(J48*N48*60)</f>
         <v/>
@@ -2440,23 +3160,49 @@
       <c r="S48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 39</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
+      <c r="B49" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
+      <c r="M49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O49" s="8">
         <f>3600*M49*H49*I49*K49/(J49*N49*60)</f>
         <v/>
@@ -2467,23 +3213,49 @@
       <c r="S49" s="8" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 40</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="9" t="n"/>
-      <c r="E50" s="9" t="n"/>
+      <c r="B50" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
+      <c r="M50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O50" s="9">
         <f>3600*M50*H50*I50*K50/(J50*N50*60)</f>
         <v/>
@@ -2494,23 +3266,49 @@
       <c r="S50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 41</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
+      <c r="B51" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
-      <c r="N51" s="7" t="n"/>
+      <c r="M51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O51" s="7">
         <f>3600*M51*H51*I51*K51/(J51*N51*60)</f>
         <v/>
@@ -2521,23 +3319,49 @@
       <c r="S51" s="7" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 42</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
+      <c r="B52" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L52" s="8" t="n"/>
-      <c r="M52" s="8" t="n"/>
-      <c r="N52" s="8" t="n"/>
+      <c r="M52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O52" s="8">
         <f>3600*M52*H52*I52*K52/(J52*N52*60)</f>
         <v/>
@@ -2548,23 +3372,49 @@
       <c r="S52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 43</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
+      <c r="B53" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L53" s="8" t="n"/>
-      <c r="M53" s="8" t="n"/>
-      <c r="N53" s="8" t="n"/>
+      <c r="M53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O53" s="8">
         <f>3600*M53*H53*I53*K53/(J53*N53*60)</f>
         <v/>
@@ -2575,23 +3425,49 @@
       <c r="S53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 44</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
+      <c r="B54" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K54" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L54" s="8" t="n"/>
-      <c r="M54" s="8" t="n"/>
-      <c r="N54" s="8" t="n"/>
+      <c r="M54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O54" s="8">
         <f>3600*M54*H54*I54*K54/(J54*N54*60)</f>
         <v/>
@@ -2602,23 +3478,49 @@
       <c r="S54" s="8" t="n"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 45</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
+      <c r="B55" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L55" s="9" t="n"/>
-      <c r="M55" s="9" t="n"/>
-      <c r="N55" s="9" t="n"/>
+      <c r="M55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O55" s="9">
         <f>3600*M55*H55*I55*K55/(J55*N55*60)</f>
         <v/>
@@ -2629,23 +3531,49 @@
       <c r="S55" s="9" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 46</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
+      <c r="B56" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-      <c r="J56" s="7" t="n"/>
-      <c r="K56" s="7" t="n"/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L56" s="7" t="n"/>
-      <c r="M56" s="7" t="n"/>
-      <c r="N56" s="7" t="n"/>
+      <c r="M56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O56" s="7">
         <f>3600*M56*H56*I56*K56/(J56*N56*60)</f>
         <v/>
@@ -2656,23 +3584,49 @@
       <c r="S56" s="7" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 47</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
+      <c r="B57" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8" t="n"/>
-      <c r="N57" s="8" t="n"/>
+      <c r="M57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O57" s="8">
         <f>3600*M57*H57*I57*K57/(J57*N57*60)</f>
         <v/>
@@ -2683,23 +3637,49 @@
       <c r="S57" s="8" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 48</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
+      <c r="B58" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J58" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K58" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L58" s="8" t="n"/>
-      <c r="M58" s="8" t="n"/>
-      <c r="N58" s="8" t="n"/>
+      <c r="M58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O58" s="8">
         <f>3600*M58*H58*I58*K58/(J58*N58*60)</f>
         <v/>
@@ -2710,23 +3690,49 @@
       <c r="S58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 49</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
+      <c r="B59" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L59" s="8" t="n"/>
-      <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
+      <c r="M59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O59" s="8">
         <f>3600*M59*H59*I59*K59/(J59*N59*60)</f>
         <v/>
@@ -2737,23 +3743,49 @@
       <c r="S59" s="8" t="n"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 50</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="9" t="n"/>
-      <c r="E60" s="9" t="n"/>
+      <c r="B60" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
-      <c r="I60" s="9" t="n"/>
-      <c r="J60" s="9" t="n"/>
-      <c r="K60" s="9" t="n"/>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L60" s="9" t="n"/>
-      <c r="M60" s="9" t="n"/>
-      <c r="N60" s="9" t="n"/>
+      <c r="M60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O60" s="9">
         <f>3600*M60*H60*I60*K60/(J60*N60*60)</f>
         <v/>
@@ -2764,23 +3796,49 @@
       <c r="S60" s="9" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 51</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
+      <c r="B61" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
-      <c r="N61" s="7" t="n"/>
+      <c r="M61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O61" s="7">
         <f>3600*M61*H61*I61*K61/(J61*N61*60)</f>
         <v/>
@@ -2791,23 +3849,49 @@
       <c r="S61" s="7" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 52</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
+      <c r="B62" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J62" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K62" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L62" s="8" t="n"/>
-      <c r="M62" s="8" t="n"/>
-      <c r="N62" s="8" t="n"/>
+      <c r="M62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O62" s="8">
         <f>3600*M62*H62*I62*K62/(J62*N62*60)</f>
         <v/>
@@ -2818,23 +3902,49 @@
       <c r="S62" s="8" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 53</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
+      <c r="B63" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K63" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L63" s="8" t="n"/>
-      <c r="M63" s="8" t="n"/>
-      <c r="N63" s="8" t="n"/>
+      <c r="M63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O63" s="8">
         <f>3600*M63*H63*I63*K63/(J63*N63*60)</f>
         <v/>
@@ -2845,23 +3955,49 @@
       <c r="S63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 54</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
+      <c r="B64" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K64" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L64" s="8" t="n"/>
-      <c r="M64" s="8" t="n"/>
-      <c r="N64" s="8" t="n"/>
+      <c r="M64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O64" s="8">
         <f>3600*M64*H64*I64*K64/(J64*N64*60)</f>
         <v/>
@@ -2872,23 +4008,49 @@
       <c r="S64" s="8" t="n"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 55</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
+      <c r="B65" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L65" s="9" t="n"/>
-      <c r="M65" s="9" t="n"/>
-      <c r="N65" s="9" t="n"/>
+      <c r="M65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O65" s="9">
         <f>3600*M65*H65*I65*K65/(J65*N65*60)</f>
         <v/>
@@ -2899,23 +4061,49 @@
       <c r="S65" s="9" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 56</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="7" t="n"/>
+      <c r="B66" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="n"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
-      <c r="N66" s="7" t="n"/>
+      <c r="M66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O66" s="7">
         <f>3600*M66*H66*I66*K66/(J66*N66*60)</f>
         <v/>
@@ -2926,23 +4114,49 @@
       <c r="S66" s="7" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 57</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
-      <c r="E67" s="8" t="n"/>
+      <c r="B67" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F67" s="8" t="n"/>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="8" t="n"/>
-      <c r="J67" s="8" t="n"/>
-      <c r="K67" s="8" t="n"/>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K67" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
+      <c r="M67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O67" s="8">
         <f>3600*M67*H67*I67*K67/(J67*N67*60)</f>
         <v/>
@@ -2953,23 +4167,49 @@
       <c r="S67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 58</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
+      <c r="B68" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F68" s="8" t="n"/>
-      <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="8" t="n"/>
-      <c r="J68" s="8" t="n"/>
-      <c r="K68" s="8" t="n"/>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K68" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L68" s="8" t="n"/>
-      <c r="M68" s="8" t="n"/>
-      <c r="N68" s="8" t="n"/>
+      <c r="M68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O68" s="8">
         <f>3600*M68*H68*I68*K68/(J68*N68*60)</f>
         <v/>
@@ -2980,23 +4220,49 @@
       <c r="S68" s="8" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 59</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
-      <c r="E69" s="8" t="n"/>
+      <c r="B69" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="8" t="n"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K69" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8" t="n"/>
-      <c r="N69" s="8" t="n"/>
+      <c r="M69" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O69" s="8">
         <f>3600*M69*H69*I69*K69/(J69*N69*60)</f>
         <v/>
@@ -3007,23 +4273,49 @@
       <c r="S69" s="8" t="n"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 60</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="9" t="n"/>
-      <c r="E70" s="9" t="n"/>
+      <c r="B70" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="9" t="n"/>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I70" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L70" s="9" t="n"/>
-      <c r="M70" s="9" t="n"/>
-      <c r="N70" s="9" t="n"/>
+      <c r="M70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O70" s="9">
         <f>3600*M70*H70*I70*K70/(J70*N70*60)</f>
         <v/>
@@ -3034,23 +4326,49 @@
       <c r="S70" s="9" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 61</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
-      <c r="E71" s="7" t="n"/>
+      <c r="B71" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F71" s="7" t="n"/>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
-      <c r="J71" s="7" t="n"/>
-      <c r="K71" s="7" t="n"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L71" s="7" t="n"/>
-      <c r="M71" s="7" t="n"/>
-      <c r="N71" s="7" t="n"/>
+      <c r="M71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O71" s="7">
         <f>3600*M71*H71*I71*K71/(J71*N71*60)</f>
         <v/>
@@ -3061,23 +4379,49 @@
       <c r="S71" s="7" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 62</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
+      <c r="B72" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F72" s="8" t="n"/>
-      <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="8" t="n"/>
-      <c r="J72" s="8" t="n"/>
-      <c r="K72" s="8" t="n"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K72" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L72" s="8" t="n"/>
-      <c r="M72" s="8" t="n"/>
-      <c r="N72" s="8" t="n"/>
+      <c r="M72" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O72" s="8">
         <f>3600*M72*H72*I72*K72/(J72*N72*60)</f>
         <v/>
@@ -3088,23 +4432,49 @@
       <c r="S72" s="8" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 63</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
+      <c r="B73" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="n"/>
-      <c r="K73" s="8" t="n"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L73" s="8" t="n"/>
-      <c r="M73" s="8" t="n"/>
-      <c r="N73" s="8" t="n"/>
+      <c r="M73" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O73" s="8">
         <f>3600*M73*H73*I73*K73/(J73*N73*60)</f>
         <v/>
@@ -3115,23 +4485,49 @@
       <c r="S73" s="8" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 64</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
+      <c r="B74" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="8" t="n"/>
-      <c r="J74" s="8" t="n"/>
-      <c r="K74" s="8" t="n"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K74" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L74" s="8" t="n"/>
-      <c r="M74" s="8" t="n"/>
-      <c r="N74" s="8" t="n"/>
+      <c r="M74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O74" s="8">
         <f>3600*M74*H74*I74*K74/(J74*N74*60)</f>
         <v/>
@@ -3142,23 +4538,49 @@
       <c r="S74" s="8" t="n"/>
     </row>
     <row r="75" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 65</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
+      <c r="B75" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L75" s="9" t="n"/>
-      <c r="M75" s="9" t="n"/>
-      <c r="N75" s="9" t="n"/>
+      <c r="M75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O75" s="9">
         <f>3600*M75*H75*I75*K75/(J75*N75*60)</f>
         <v/>
@@ -3169,23 +4591,49 @@
       <c r="S75" s="9" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 66</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="7" t="n"/>
+      <c r="B76" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-      <c r="K76" s="7" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L76" s="7" t="n"/>
-      <c r="M76" s="7" t="n"/>
-      <c r="N76" s="7" t="n"/>
+      <c r="M76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O76" s="7">
         <f>3600*M76*H76*I76*K76/(J76*N76*60)</f>
         <v/>
@@ -3196,23 +4644,49 @@
       <c r="S76" s="7" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 67</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
+      <c r="B77" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="8" t="n"/>
-      <c r="J77" s="8" t="n"/>
-      <c r="K77" s="8" t="n"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K77" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L77" s="8" t="n"/>
-      <c r="M77" s="8" t="n"/>
-      <c r="N77" s="8" t="n"/>
+      <c r="M77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O77" s="8">
         <f>3600*M77*H77*I77*K77/(J77*N77*60)</f>
         <v/>
@@ -3223,23 +4697,49 @@
       <c r="S77" s="8" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 68</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
+      <c r="B78" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K78" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L78" s="8" t="n"/>
-      <c r="M78" s="8" t="n"/>
-      <c r="N78" s="8" t="n"/>
+      <c r="M78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O78" s="8">
         <f>3600*M78*H78*I78*K78/(J78*N78*60)</f>
         <v/>
@@ -3250,23 +4750,49 @@
       <c r="S78" s="8" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 69</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
-      <c r="E79" s="8" t="n"/>
+      <c r="B79" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="8" t="n"/>
-      <c r="J79" s="8" t="n"/>
-      <c r="K79" s="8" t="n"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K79" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L79" s="8" t="n"/>
-      <c r="M79" s="8" t="n"/>
-      <c r="N79" s="8" t="n"/>
+      <c r="M79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O79" s="8">
         <f>3600*M79*H79*I79*K79/(J79*N79*60)</f>
         <v/>
@@ -3277,23 +4803,49 @@
       <c r="S79" s="8" t="n"/>
     </row>
     <row r="80" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 70</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
+      <c r="B80" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="9" t="n"/>
-      <c r="I80" s="9" t="n"/>
-      <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I80" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L80" s="9" t="n"/>
-      <c r="M80" s="9" t="n"/>
-      <c r="N80" s="9" t="n"/>
+      <c r="M80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O80" s="9">
         <f>3600*M80*H80*I80*K80/(J80*N80*60)</f>
         <v/>
@@ -3304,23 +4856,49 @@
       <c r="S80" s="9" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 71</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
-      <c r="E81" s="7" t="n"/>
+      <c r="B81" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="n"/>
-      <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
-      <c r="J81" s="7" t="n"/>
-      <c r="K81" s="7" t="n"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L81" s="7" t="n"/>
-      <c r="M81" s="7" t="n"/>
-      <c r="N81" s="7" t="n"/>
+      <c r="M81" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O81" s="7">
         <f>3600*M81*H81*I81*K81/(J81*N81*60)</f>
         <v/>
@@ -3331,23 +4909,49 @@
       <c r="S81" s="7" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 72</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
+      <c r="B82" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="8" t="n"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J82" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K82" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L82" s="8" t="n"/>
-      <c r="M82" s="8" t="n"/>
-      <c r="N82" s="8" t="n"/>
+      <c r="M82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O82" s="8">
         <f>3600*M82*H82*I82*K82/(J82*N82*60)</f>
         <v/>
@@ -3358,23 +4962,49 @@
       <c r="S82" s="8" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 73</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
+      <c r="B83" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="8" t="n"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J83" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K83" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L83" s="8" t="n"/>
-      <c r="M83" s="8" t="n"/>
-      <c r="N83" s="8" t="n"/>
+      <c r="M83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O83" s="8">
         <f>3600*M83*H83*I83*K83/(J83*N83*60)</f>
         <v/>
@@ -3385,23 +5015,49 @@
       <c r="S83" s="8" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 74</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
+      <c r="B84" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J84" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K84" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L84" s="8" t="n"/>
-      <c r="M84" s="8" t="n"/>
-      <c r="N84" s="8" t="n"/>
+      <c r="M84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O84" s="8">
         <f>3600*M84*H84*I84*K84/(J84*N84*60)</f>
         <v/>
@@ -3412,23 +5068,49 @@
       <c r="S84" s="8" t="n"/>
     </row>
     <row r="85" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 75</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
+      <c r="B85" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="n"/>
-      <c r="J85" s="9" t="n"/>
-      <c r="K85" s="9" t="n"/>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I85" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L85" s="9" t="n"/>
-      <c r="M85" s="9" t="n"/>
-      <c r="N85" s="9" t="n"/>
+      <c r="M85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O85" s="9">
         <f>3600*M85*H85*I85*K85/(J85*N85*60)</f>
         <v/>
@@ -3439,23 +5121,49 @@
       <c r="S85" s="9" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 76</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="7" t="n"/>
+      <c r="B86" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
-      <c r="K86" s="7" t="n"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L86" s="7" t="n"/>
-      <c r="M86" s="7" t="n"/>
-      <c r="N86" s="7" t="n"/>
+      <c r="M86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O86" s="7">
         <f>3600*M86*H86*I86*K86/(J86*N86*60)</f>
         <v/>
@@ -3466,23 +5174,49 @@
       <c r="S86" s="7" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 77</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="8" t="n"/>
+      <c r="B87" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
-      <c r="J87" s="8" t="n"/>
-      <c r="K87" s="8" t="n"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J87" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K87" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L87" s="8" t="n"/>
-      <c r="M87" s="8" t="n"/>
-      <c r="N87" s="8" t="n"/>
+      <c r="M87" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O87" s="8">
         <f>3600*M87*H87*I87*K87/(J87*N87*60)</f>
         <v/>
@@ -3493,23 +5227,49 @@
       <c r="S87" s="8" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 78</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="8" t="n"/>
+      <c r="B88" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-      <c r="J88" s="8" t="n"/>
-      <c r="K88" s="8" t="n"/>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J88" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K88" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
-      <c r="N88" s="8" t="n"/>
+      <c r="M88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O88" s="8">
         <f>3600*M88*H88*I88*K88/(J88*N88*60)</f>
         <v/>
@@ -3520,23 +5280,49 @@
       <c r="S88" s="8" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 79</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
+      <c r="B89" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="8" t="n"/>
-      <c r="J89" s="8" t="n"/>
-      <c r="K89" s="8" t="n"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J89" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K89" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
+      <c r="M89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O89" s="8">
         <f>3600*M89*H89*I89*K89/(J89*N89*60)</f>
         <v/>
@@ -3547,23 +5333,49 @@
       <c r="S89" s="8" t="n"/>
     </row>
     <row r="90" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 80</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
+      <c r="B90" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="n"/>
-      <c r="J90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L90" s="9" t="n"/>
-      <c r="M90" s="9" t="n"/>
-      <c r="N90" s="9" t="n"/>
+      <c r="M90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O90" s="9">
         <f>3600*M90*H90*I90*K90/(J90*N90*60)</f>
         <v/>
@@ -3574,23 +5386,49 @@
       <c r="S90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 81</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
+      <c r="B91" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L91" s="7" t="n"/>
-      <c r="M91" s="7" t="n"/>
-      <c r="N91" s="7" t="n"/>
+      <c r="M91" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O91" s="7">
         <f>3600*M91*H91*I91*K91/(J91*N91*60)</f>
         <v/>
@@ -3601,23 +5439,49 @@
       <c r="S91" s="7" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 82</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
-      <c r="E92" s="8" t="n"/>
+      <c r="B92" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F92" s="8" t="n"/>
-      <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="8" t="n"/>
-      <c r="J92" s="8" t="n"/>
-      <c r="K92" s="8" t="n"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J92" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K92" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L92" s="8" t="n"/>
-      <c r="M92" s="8" t="n"/>
-      <c r="N92" s="8" t="n"/>
+      <c r="M92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O92" s="8">
         <f>3600*M92*H92*I92*K92/(J92*N92*60)</f>
         <v/>
@@ -3628,23 +5492,49 @@
       <c r="S92" s="8" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 83</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="8" t="n"/>
+      <c r="B93" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
-      <c r="J93" s="8" t="n"/>
-      <c r="K93" s="8" t="n"/>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J93" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K93" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8" t="n"/>
-      <c r="N93" s="8" t="n"/>
+      <c r="M93" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O93" s="8">
         <f>3600*M93*H93*I93*K93/(J93*N93*60)</f>
         <v/>
@@ -3655,23 +5545,49 @@
       <c r="S93" s="8" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 84</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
+      <c r="B94" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
-      <c r="J94" s="8" t="n"/>
-      <c r="K94" s="8" t="n"/>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I94" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J94" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K94" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L94" s="8" t="n"/>
-      <c r="M94" s="8" t="n"/>
-      <c r="N94" s="8" t="n"/>
+      <c r="M94" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O94" s="8">
         <f>3600*M94*H94*I94*K94/(J94*N94*60)</f>
         <v/>
@@ -3682,23 +5598,49 @@
       <c r="S94" s="8" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 85</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="9" t="n"/>
+      <c r="B95" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="n"/>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L95" s="9" t="n"/>
-      <c r="M95" s="9" t="n"/>
-      <c r="N95" s="9" t="n"/>
+      <c r="M95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O95" s="9">
         <f>3600*M95*H95*I95*K95/(J95*N95*60)</f>
         <v/>
@@ -3709,23 +5651,49 @@
       <c r="S95" s="9" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 86</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
-      <c r="E96" s="7" t="n"/>
+      <c r="B96" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="7" t="n"/>
-      <c r="K96" s="7" t="n"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L96" s="7" t="n"/>
-      <c r="M96" s="7" t="n"/>
-      <c r="N96" s="7" t="n"/>
+      <c r="M96" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O96" s="7">
         <f>3600*M96*H96*I96*K96/(J96*N96*60)</f>
         <v/>
@@ -3736,23 +5704,49 @@
       <c r="S96" s="7" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 87</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="8" t="n"/>
+      <c r="B97" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
-      <c r="J97" s="8" t="n"/>
-      <c r="K97" s="8" t="n"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J97" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K97" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8" t="n"/>
-      <c r="N97" s="8" t="n"/>
+      <c r="M97" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O97" s="8">
         <f>3600*M97*H97*I97*K97/(J97*N97*60)</f>
         <v/>
@@ -3763,23 +5757,49 @@
       <c r="S97" s="8" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 88</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
+      <c r="B98" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="8" t="n"/>
-      <c r="K98" s="8" t="n"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I98" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J98" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K98" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L98" s="8" t="n"/>
-      <c r="M98" s="8" t="n"/>
-      <c r="N98" s="8" t="n"/>
+      <c r="M98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O98" s="8">
         <f>3600*M98*H98*I98*K98/(J98*N98*60)</f>
         <v/>
@@ -3790,23 +5810,49 @@
       <c r="S98" s="8" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 89</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
-      <c r="E99" s="8" t="n"/>
+      <c r="B99" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
-      <c r="J99" s="8" t="n"/>
-      <c r="K99" s="8" t="n"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K99" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L99" s="8" t="n"/>
-      <c r="M99" s="8" t="n"/>
-      <c r="N99" s="8" t="n"/>
+      <c r="M99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O99" s="8">
         <f>3600*M99*H99*I99*K99/(J99*N99*60)</f>
         <v/>
@@ -3817,23 +5863,49 @@
       <c r="S99" s="8" t="n"/>
     </row>
     <row r="100" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 90</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="n"/>
-      <c r="D100" s="9" t="n"/>
-      <c r="E100" s="9" t="n"/>
+      <c r="B100" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F100" s="9" t="n"/>
-      <c r="G100" s="9" t="n"/>
-      <c r="H100" s="9" t="n"/>
-      <c r="I100" s="9" t="n"/>
-      <c r="J100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L100" s="9" t="n"/>
-      <c r="M100" s="9" t="n"/>
-      <c r="N100" s="9" t="n"/>
+      <c r="M100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O100" s="9">
         <f>3600*M100*H100*I100*K100/(J100*N100*60)</f>
         <v/>
@@ -3844,23 +5916,49 @@
       <c r="S100" s="9" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 91</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
-      <c r="E101" s="7" t="n"/>
+      <c r="B101" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F101" s="7" t="n"/>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
-      <c r="J101" s="7" t="n"/>
-      <c r="K101" s="7" t="n"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J101" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L101" s="7" t="n"/>
-      <c r="M101" s="7" t="n"/>
-      <c r="N101" s="7" t="n"/>
+      <c r="M101" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O101" s="7">
         <f>3600*M101*H101*I101*K101/(J101*N101*60)</f>
         <v/>
@@ -3871,23 +5969,49 @@
       <c r="S101" s="7" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 92</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
+      <c r="B102" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F102" s="8" t="n"/>
-      <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="8" t="n"/>
-      <c r="K102" s="8" t="n"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I102" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J102" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K102" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L102" s="8" t="n"/>
-      <c r="M102" s="8" t="n"/>
-      <c r="N102" s="8" t="n"/>
+      <c r="M102" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O102" s="8">
         <f>3600*M102*H102*I102*K102/(J102*N102*60)</f>
         <v/>
@@ -3898,23 +6022,49 @@
       <c r="S102" s="8" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 93</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
+      <c r="B103" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
-      <c r="J103" s="8" t="n"/>
-      <c r="K103" s="8" t="n"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I103" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J103" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K103" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L103" s="8" t="n"/>
-      <c r="M103" s="8" t="n"/>
-      <c r="N103" s="8" t="n"/>
+      <c r="M103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O103" s="8">
         <f>3600*M103*H103*I103*K103/(J103*N103*60)</f>
         <v/>
@@ -3925,23 +6075,49 @@
       <c r="S103" s="8" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 94</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="8" t="n"/>
+      <c r="B104" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F104" s="8" t="n"/>
-      <c r="G104" s="8" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
-      <c r="J104" s="8" t="n"/>
-      <c r="K104" s="8" t="n"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I104" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J104" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K104" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L104" s="8" t="n"/>
-      <c r="M104" s="8" t="n"/>
-      <c r="N104" s="8" t="n"/>
+      <c r="M104" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O104" s="8">
         <f>3600*M104*H104*I104*K104/(J104*N104*60)</f>
         <v/>
@@ -3952,23 +6128,49 @@
       <c r="S104" s="8" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 95</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
+      <c r="B105" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L105" s="9" t="n"/>
-      <c r="M105" s="9" t="n"/>
-      <c r="N105" s="9" t="n"/>
+      <c r="M105" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O105" s="9">
         <f>3600*M105*H105*I105*K105/(J105*N105*60)</f>
         <v/>
@@ -3979,23 +6181,49 @@
       <c r="S105" s="9" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Exacator 96</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="n"/>
-      <c r="E106" s="7" t="n"/>
+      <c r="B106" s="7" t="n">
+        <v>505</v>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="n"/>
-      <c r="G106" s="7" t="n"/>
-      <c r="H106" s="7" t="n"/>
-      <c r="I106" s="7" t="n"/>
-      <c r="J106" s="7" t="n"/>
-      <c r="K106" s="7" t="n"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J106" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="L106" s="7" t="n"/>
-      <c r="M106" s="7" t="n"/>
-      <c r="N106" s="7" t="n"/>
+      <c r="M106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" s="7" t="n">
+        <v>263</v>
+      </c>
       <c r="O106" s="7">
         <f>3600*M106*H106*I106*K106/(J106*N106*60)</f>
         <v/>
@@ -4006,23 +6234,49 @@
       <c r="S106" s="7" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 97</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
+      <c r="B107" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I107" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J107" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K107" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L107" s="8" t="n"/>
-      <c r="M107" s="8" t="n"/>
-      <c r="N107" s="8" t="n"/>
+      <c r="M107" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O107" s="8">
         <f>3600*M107*H107*I107*K107/(J107*N107*60)</f>
         <v/>
@@ -4033,23 +6287,49 @@
       <c r="S107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 98</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
+      <c r="B108" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I108" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J108" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K108" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L108" s="8" t="n"/>
-      <c r="M108" s="8" t="n"/>
-      <c r="N108" s="8" t="n"/>
+      <c r="M108" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O108" s="8">
         <f>3600*M108*H108*I108*K108/(J108*N108*60)</f>
         <v/>
@@ -4060,23 +6340,49 @@
       <c r="S108" s="8" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Exacator 99</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
+      <c r="B109" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
-      <c r="J109" s="8" t="n"/>
-      <c r="K109" s="8" t="n"/>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I109" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J109" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K109" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="L109" s="8" t="n"/>
-      <c r="M109" s="8" t="n"/>
-      <c r="N109" s="8" t="n"/>
+      <c r="M109" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="8" t="n">
+        <v>263</v>
+      </c>
       <c r="O109" s="8">
         <f>3600*M109*H109*I109*K109/(J109*N109*60)</f>
         <v/>
@@ -4087,23 +6393,49 @@
       <c r="S109" s="8" t="n"/>
     </row>
     <row r="110" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Exacator 100</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="n"/>
-      <c r="D110" s="9" t="n"/>
-      <c r="E110" s="9" t="n"/>
+      <c r="B110" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/10 foreman 1 helper, 1 operator </t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>01 rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
       <c r="F110" s="9" t="n"/>
-      <c r="G110" s="9" t="n"/>
-      <c r="H110" s="9" t="n"/>
-      <c r="I110" s="9" t="n"/>
-      <c r="J110" s="9" t="n"/>
-      <c r="K110" s="9" t="n"/>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I110" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>60</v>
+      </c>
       <c r="L110" s="9" t="n"/>
-      <c r="M110" s="9" t="n"/>
-      <c r="N110" s="9" t="n"/>
+      <c r="M110" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" s="9" t="n">
+        <v>263</v>
+      </c>
       <c r="O110" s="9">
         <f>3600*M110*H110*I110*K110/(J110*N110*60)</f>
         <v/>

--- a/P012-excavator-split_data_files/output/17_22_05_2017_template.xlsx
+++ b/P012-excavator-split_data_files/output/17_22_05_2017_template.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6945" yWindow="2085" windowWidth="20490" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excavator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPDM 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPDM" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Excavator'!$A$1:$S$111</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'MPDM 1'!$A$1:$T$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'MPDM'!$A$1:$T$120</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" concurrentCalc="0"/>
 </workbook>
@@ -56,10 +56,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -343,12 +345,12 @@
     </border>
   </borders>
   <cellStyleXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -470,11 +472,11 @@
     <xf numFmtId="9" fontId="3" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -494,6 +496,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -504,19 +515,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -525,9 +524,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -997,10 +993,14 @@
           <t>Number of Equipment Types:</t>
         </is>
       </c>
-      <c r="H6" s="57" t="n"/>
+      <c r="H6" s="56" t="n"/>
       <c r="I6" s="48" t="n"/>
       <c r="J6" s="2" t="n"/>
-      <c r="L6" s="47" t="n"/>
+      <c r="L6" s="47" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
@@ -1018,92 +1018,92 @@
       <c r="O8" s="5" t="n"/>
     </row>
     <row r="9" ht="32.25" customHeight="1" thickBot="1">
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="57" t="inlineStr">
         <is>
           <t>Equipment Tag</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>Manpower (Foreman, Operator, Helper, Laborers, etc.)</t>
         </is>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>Excavator Type (Face Shovel, Hoe, Loader)</t>
         </is>
       </c>
-      <c r="E9" s="58" t="inlineStr">
+      <c r="E9" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Task Type </t>
         </is>
       </c>
-      <c r="F9" s="58" t="inlineStr">
+      <c r="F9" s="57" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G9" s="58" t="inlineStr">
+      <c r="G9" s="57" t="inlineStr">
         <is>
           <t>Soil Type</t>
         </is>
       </c>
-      <c r="H9" s="58" t="inlineStr">
+      <c r="H9" s="57" t="inlineStr">
         <is>
           <t>Factors</t>
         </is>
       </c>
-      <c r="I9" s="59" t="n"/>
-      <c r="J9" s="59" t="n"/>
-      <c r="K9" s="57" t="n"/>
-      <c r="L9" s="58" t="inlineStr">
+      <c r="I9" s="58" t="n"/>
+      <c r="J9" s="58" t="n"/>
+      <c r="K9" s="56" t="n"/>
+      <c r="L9" s="57" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="M9" s="58" t="inlineStr">
+      <c r="M9" s="57" t="inlineStr">
         <is>
           <t>Q Heaped Bucket Capcity</t>
         </is>
       </c>
-      <c r="N9" s="58" t="inlineStr">
+      <c r="N9" s="57" t="inlineStr">
         <is>
           <t>T Cycle Time (seconds)</t>
         </is>
       </c>
-      <c r="O9" s="58" t="inlineStr">
+      <c r="O9" s="57" t="inlineStr">
         <is>
           <t>Productivity (m3/hr)</t>
         </is>
       </c>
-      <c r="P9" s="58" t="inlineStr">
+      <c r="P9" s="57" t="inlineStr">
         <is>
           <t>Ideal Productivity (m3/hr)</t>
         </is>
       </c>
-      <c r="Q9" s="58" t="inlineStr">
+      <c r="Q9" s="57" t="inlineStr">
         <is>
           <t>Overall Method Productivity (m3/hr)</t>
         </is>
       </c>
-      <c r="R9" s="58" t="inlineStr">
+      <c r="R9" s="57" t="inlineStr">
         <is>
           <t>Ideal Cycle Variability (%)</t>
         </is>
       </c>
-      <c r="S9" s="58" t="inlineStr">
+      <c r="S9" s="57" t="inlineStr">
         <is>
           <t>Overall Cycle Vairability (%)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42.75" customHeight="1" thickBot="1">
-      <c r="B10" s="60" t="n"/>
-      <c r="C10" s="60" t="n"/>
-      <c r="D10" s="60" t="n"/>
-      <c r="E10" s="60" t="n"/>
-      <c r="F10" s="60" t="n"/>
-      <c r="G10" s="60" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
           <t>F (Bucket Fill Factor)</t>
@@ -1124,14 +1124,14 @@
           <t xml:space="preserve">Efficiency </t>
         </is>
       </c>
-      <c r="L10" s="60" t="n"/>
-      <c r="M10" s="60" t="n"/>
-      <c r="N10" s="60" t="n"/>
-      <c r="O10" s="60" t="n"/>
-      <c r="P10" s="60" t="n"/>
-      <c r="Q10" s="60" t="n"/>
-      <c r="R10" s="60" t="n"/>
-      <c r="S10" s="60" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
+      <c r="P10" s="59" t="n"/>
+      <c r="Q10" s="59" t="n"/>
+      <c r="R10" s="59" t="n"/>
+      <c r="S10" s="59" t="n"/>
     </row>
     <row r="11" ht="33" customHeight="1">
       <c r="B11" s="7" t="n">
@@ -1182,19 +1182,19 @@
         <v/>
       </c>
       <c r="P11" s="39">
-        <f>'MPDM 1'!H118*H11*I11*J11*M11</f>
+        <f>MPDM!H118*H11*I11*J11*M11</f>
         <v/>
       </c>
       <c r="Q11" s="39">
-        <f>'MPDM 1'!K118*H11*I11*J11*M11</f>
+        <f>MPDM!K118*H11*I11*J11*M11</f>
         <v/>
       </c>
       <c r="R11" s="40">
-        <f>'MPDM 1'!H119</f>
+        <f>MPDM!H119</f>
         <v/>
       </c>
       <c r="S11" s="40">
-        <f>'MPDM 1'!K119</f>
+        <f>MPDM!K119</f>
         <v/>
       </c>
     </row>
@@ -6446,16 +6446,16 @@
       <c r="S110" s="9" t="n"/>
     </row>
     <row r="111" customFormat="1" s="5">
-      <c r="B111" s="56" t="inlineStr">
+      <c r="B111" s="49" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="C111" s="61" t="n"/>
-      <c r="D111" s="61" t="n"/>
-      <c r="E111" s="61" t="n"/>
-      <c r="F111" s="61" t="n"/>
-      <c r="G111" s="61" t="n"/>
+      <c r="C111" s="60" t="n"/>
+      <c r="D111" s="60" t="n"/>
+      <c r="E111" s="60" t="n"/>
+      <c r="F111" s="60" t="n"/>
+      <c r="G111" s="60" t="n"/>
       <c r="H111" s="5">
         <f>AVERAGE(H11:H110)</f>
         <v/>
@@ -6497,8 +6497,8 @@
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="S9:S10"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B9:B10"/>
     <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="H9:K9"/>
     <mergeCell ref="L9:L10"/>
@@ -6586,15 +6586,19 @@
           <t>Project Code:</t>
         </is>
       </c>
-      <c r="B6" s="62" t="n"/>
-      <c r="C6" s="57" t="n"/>
+      <c r="B6" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G6" s="53" t="n">
-        <v>1</v>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>22_05_2017</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1" thickBot="1"/>
@@ -6604,14 +6608,14 @@
           <t>Operation/Activity:</t>
         </is>
       </c>
-      <c r="B8" s="62" t="n"/>
-      <c r="C8" s="57" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="2" t="n"/>
       <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Unit of Time:</t>
         </is>
       </c>
-      <c r="G8" s="53" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Seconds</t>
         </is>
@@ -6623,63 +6627,67 @@
           <t>Equipment Type:</t>
         </is>
       </c>
-      <c r="B9" s="62" t="n"/>
-      <c r="C9" s="57" t="n"/>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>excavator</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" thickBot="1">
       <c r="A10" s="20" t="n"/>
       <c r="B10" s="20" t="n"/>
     </row>
     <row r="11" ht="32.25" customHeight="1" thickBot="1">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="57" t="inlineStr">
         <is>
           <t>Production Cycle Number</t>
         </is>
       </c>
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>Cycle Time (Seconds)</t>
         </is>
       </c>
-      <c r="C11" s="58" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>Delay (Insert Delay us 1 or if more than one delay event a proportion of the delay). Leave zero values as BLANK</t>
         </is>
       </c>
-      <c r="D11" s="59" t="n"/>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="59" t="n"/>
-      <c r="G11" s="59" t="n"/>
-      <c r="H11" s="57" t="n"/>
-      <c r="I11" s="51" t="n"/>
-      <c r="J11" s="51" t="n"/>
-      <c r="K11" s="51" t="n"/>
-      <c r="L11" s="51" t="n"/>
+      <c r="D11" s="58" t="n"/>
+      <c r="E11" s="58" t="n"/>
+      <c r="F11" s="58" t="n"/>
+      <c r="G11" s="58" t="n"/>
+      <c r="H11" s="56" t="n"/>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="54" t="n"/>
+      <c r="L11" s="54" t="n"/>
       <c r="M11" s="21" t="n"/>
-      <c r="O11" s="58" t="inlineStr">
+      <c r="O11" s="57" t="inlineStr">
         <is>
           <t>Delay (Time)</t>
         </is>
       </c>
-      <c r="P11" s="59" t="n"/>
-      <c r="Q11" s="59" t="n"/>
-      <c r="R11" s="59" t="n"/>
-      <c r="S11" s="59" t="n"/>
-      <c r="T11" s="57" t="n"/>
-      <c r="V11" s="58" t="inlineStr">
+      <c r="P11" s="58" t="n"/>
+      <c r="Q11" s="58" t="n"/>
+      <c r="R11" s="58" t="n"/>
+      <c r="S11" s="58" t="n"/>
+      <c r="T11" s="56" t="n"/>
+      <c r="V11" s="57" t="inlineStr">
         <is>
           <t>Delay (Time)</t>
         </is>
       </c>
-      <c r="W11" s="59" t="n"/>
-      <c r="X11" s="59" t="n"/>
-      <c r="Y11" s="59" t="n"/>
-      <c r="Z11" s="59" t="n"/>
-      <c r="AA11" s="57" t="n"/>
+      <c r="W11" s="58" t="n"/>
+      <c r="X11" s="58" t="n"/>
+      <c r="Y11" s="58" t="n"/>
+      <c r="Z11" s="58" t="n"/>
+      <c r="AA11" s="56" t="n"/>
     </row>
     <row r="12" ht="42.75" customHeight="1" thickBot="1">
-      <c r="A12" s="60" t="n"/>
-      <c r="B12" s="60" t="n"/>
+      <c r="A12" s="59" t="n"/>
+      <c r="B12" s="59" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Enviroment</t>
@@ -6803,27 +6811,27 @@
       <c r="B13" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="41">
         <f>IF(SUM($V13:$AA13), ROUND(V13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="41">
         <f>IF(SUM($V13:$AA13), ROUND(W13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="41">
         <f>IF(SUM($V13:$AA13), ROUND(X13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="41">
         <f>IF(SUM($V13:$AA13), ROUND(Y13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="41">
         <f>IF(SUM($V13:$AA13), ROUND(Z13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="H13" s="54">
+      <c r="H13" s="41">
         <f>IF(SUM($V13:$AA13), ROUND(AA13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
@@ -6885,27 +6893,27 @@
       <c r="B14" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="41">
         <f>IF(SUM($V14:$AA14), ROUND(V14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="41">
         <f>IF(SUM($V14:$AA14), ROUND(W14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="41">
         <f>IF(SUM($V14:$AA14), ROUND(X14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="41">
         <f>IF(SUM($V14:$AA14), ROUND(Y14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="41">
         <f>IF(SUM($V14:$AA14), ROUND(Z14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="41">
         <f>IF(SUM($V14:$AA14), ROUND(AA14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
@@ -6967,27 +6975,27 @@
       <c r="B15" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="41">
         <f>IF(SUM($V15:$AA15), ROUND(V15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="41">
         <f>IF(SUM($V15:$AA15), ROUND(W15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="41">
         <f>IF(SUM($V15:$AA15), ROUND(X15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="F15" s="54">
+      <c r="F15" s="41">
         <f>IF(SUM($V15:$AA15), ROUND(Y15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="41">
         <f>IF(SUM($V15:$AA15), ROUND(Z15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="H15" s="54">
+      <c r="H15" s="41">
         <f>IF(SUM($V15:$AA15), ROUND(AA15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
@@ -7049,27 +7057,27 @@
       <c r="B16" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="41">
         <f>IF(SUM($V16:$AA16), ROUND(V16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="41">
         <f>IF(SUM($V16:$AA16), ROUND(W16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="41">
         <f>IF(SUM($V16:$AA16), ROUND(X16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="F16" s="54">
+      <c r="F16" s="41">
         <f>IF(SUM($V16:$AA16), ROUND(Y16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="41">
         <f>IF(SUM($V16:$AA16), ROUND(Z16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="H16" s="54">
+      <c r="H16" s="41">
         <f>IF(SUM($V16:$AA16), ROUND(AA16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
@@ -7131,27 +7139,27 @@
       <c r="B17" s="26" t="n">
         <v>263</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="41">
         <f>IF(SUM($V17:$AA17), ROUND(V17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="41">
         <f>IF(SUM($V17:$AA17), ROUND(W17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="41">
         <f>IF(SUM($V17:$AA17), ROUND(X17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="41">
         <f>IF(SUM($V17:$AA17), ROUND(Y17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="41">
         <f>IF(SUM($V17:$AA17), ROUND(Z17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="H17" s="54">
+      <c r="H17" s="41">
         <f>IF(SUM($V17:$AA17), ROUND(AA17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
@@ -7215,27 +7223,27 @@
       <c r="B18" s="26" t="n">
         <v>23</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="41">
         <f>IF(SUM($V18:$AA18), ROUND(V18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="41">
         <f>IF(SUM($V18:$AA18), ROUND(W18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="41">
         <f>IF(SUM($V18:$AA18), ROUND(X18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="41">
         <f>IF(SUM($V18:$AA18), ROUND(Y18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="41">
         <f>IF(SUM($V18:$AA18), ROUND(Z18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="H18" s="54">
+      <c r="H18" s="41">
         <f>IF(SUM($V18:$AA18), ROUND(AA18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
@@ -7297,27 +7305,27 @@
       <c r="B19" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="41">
         <f>IF(SUM($V19:$AA19), ROUND(V19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="41">
         <f>IF(SUM($V19:$AA19), ROUND(W19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="41">
         <f>IF(SUM($V19:$AA19), ROUND(X19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="41">
         <f>IF(SUM($V19:$AA19), ROUND(Y19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="41">
         <f>IF(SUM($V19:$AA19), ROUND(Z19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="H19" s="54">
+      <c r="H19" s="41">
         <f>IF(SUM($V19:$AA19), ROUND(AA19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
@@ -7379,27 +7387,27 @@
       <c r="B20" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="41">
         <f>IF(SUM($V20:$AA20), ROUND(V20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="41">
         <f>IF(SUM($V20:$AA20), ROUND(W20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="41">
         <f>IF(SUM($V20:$AA20), ROUND(X20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="41">
         <f>IF(SUM($V20:$AA20), ROUND(Y20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="41">
         <f>IF(SUM($V20:$AA20), ROUND(Z20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="41">
         <f>IF(SUM($V20:$AA20), ROUND(AA20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
@@ -7461,27 +7469,27 @@
       <c r="B21" s="26" t="n">
         <v>23</v>
       </c>
-      <c r="C21" s="54">
+      <c r="C21" s="41">
         <f>IF(SUM($V21:$AA21), ROUND(V21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="41">
         <f>IF(SUM($V21:$AA21), ROUND(W21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="41">
         <f>IF(SUM($V21:$AA21), ROUND(X21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="41">
         <f>IF(SUM($V21:$AA21), ROUND(Y21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="41">
         <f>IF(SUM($V21:$AA21), ROUND(Z21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="H21" s="54">
+      <c r="H21" s="41">
         <f>IF(SUM($V21:$AA21), ROUND(AA21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
@@ -7543,27 +7551,27 @@
       <c r="B22" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C22" s="41">
         <f>IF(SUM($V22:$AA22), ROUND(V22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="41">
         <f>IF(SUM($V22:$AA22), ROUND(W22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="41">
         <f>IF(SUM($V22:$AA22), ROUND(X22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="41">
         <f>IF(SUM($V22:$AA22), ROUND(Y22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="41">
         <f>IF(SUM($V22:$AA22), ROUND(Z22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="H22" s="54">
+      <c r="H22" s="41">
         <f>IF(SUM($V22:$AA22), ROUND(AA22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
@@ -7625,27 +7633,27 @@
       <c r="B23" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="41">
         <f>IF(SUM($V23:$AA23), ROUND(V23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="D23" s="54">
+      <c r="D23" s="41">
         <f>IF(SUM($V23:$AA23), ROUND(W23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="E23" s="54">
+      <c r="E23" s="41">
         <f>IF(SUM($V23:$AA23), ROUND(X23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="41">
         <f>IF(SUM($V23:$AA23), ROUND(Y23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="G23" s="54">
+      <c r="G23" s="41">
         <f>IF(SUM($V23:$AA23), ROUND(Z23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="H23" s="54">
+      <c r="H23" s="41">
         <f>IF(SUM($V23:$AA23), ROUND(AA23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
@@ -7707,27 +7715,27 @@
       <c r="B24" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="C24" s="54">
+      <c r="C24" s="41">
         <f>IF(SUM($V24:$AA24), ROUND(V24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="41">
         <f>IF(SUM($V24:$AA24), ROUND(W24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="41">
         <f>IF(SUM($V24:$AA24), ROUND(X24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="41">
         <f>IF(SUM($V24:$AA24), ROUND(Y24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="41">
         <f>IF(SUM($V24:$AA24), ROUND(Z24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="H24" s="54">
+      <c r="H24" s="41">
         <f>IF(SUM($V24:$AA24), ROUND(AA24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
@@ -7787,27 +7795,27 @@
         <v>13</v>
       </c>
       <c r="B25" s="26" t="n"/>
-      <c r="C25" s="54">
+      <c r="C25" s="41">
         <f>IF(SUM($V25:$AA25), ROUND(V25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="41">
         <f>IF(SUM($V25:$AA25), ROUND(W25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="41">
         <f>IF(SUM($V25:$AA25), ROUND(X25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="41">
         <f>IF(SUM($V25:$AA25), ROUND(Y25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="G25" s="54">
+      <c r="G25" s="41">
         <f>IF(SUM($V25:$AA25), ROUND(Z25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="H25" s="54">
+      <c r="H25" s="41">
         <f>IF(SUM($V25:$AA25), ROUND(AA25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
@@ -7867,27 +7875,27 @@
         <v>14</v>
       </c>
       <c r="B26" s="26" t="n"/>
-      <c r="C26" s="54">
+      <c r="C26" s="41">
         <f>IF(SUM($V26:$AA26), ROUND(V26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="41">
         <f>IF(SUM($V26:$AA26), ROUND(W26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="41">
         <f>IF(SUM($V26:$AA26), ROUND(X26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="41">
         <f>IF(SUM($V26:$AA26), ROUND(Y26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="G26" s="54">
+      <c r="G26" s="41">
         <f>IF(SUM($V26:$AA26), ROUND(Z26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="H26" s="54">
+      <c r="H26" s="41">
         <f>IF(SUM($V26:$AA26), ROUND(AA26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
@@ -7947,27 +7955,27 @@
         <v>15</v>
       </c>
       <c r="B27" s="26" t="n"/>
-      <c r="C27" s="54">
+      <c r="C27" s="41">
         <f>IF(SUM($V27:$AA27), ROUND(V27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="41">
         <f>IF(SUM($V27:$AA27), ROUND(W27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="E27" s="54">
+      <c r="E27" s="41">
         <f>IF(SUM($V27:$AA27), ROUND(X27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="F27" s="54">
+      <c r="F27" s="41">
         <f>IF(SUM($V27:$AA27), ROUND(Y27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="41">
         <f>IF(SUM($V27:$AA27), ROUND(Z27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="H27" s="54">
+      <c r="H27" s="41">
         <f>IF(SUM($V27:$AA27), ROUND(AA27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
@@ -8027,27 +8035,27 @@
         <v>16</v>
       </c>
       <c r="B28" s="26" t="n"/>
-      <c r="C28" s="54">
+      <c r="C28" s="41">
         <f>IF(SUM($V28:$AA28), ROUND(V28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="41">
         <f>IF(SUM($V28:$AA28), ROUND(W28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="41">
         <f>IF(SUM($V28:$AA28), ROUND(X28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="F28" s="54">
+      <c r="F28" s="41">
         <f>IF(SUM($V28:$AA28), ROUND(Y28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="G28" s="54">
+      <c r="G28" s="41">
         <f>IF(SUM($V28:$AA28), ROUND(Z28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="H28" s="54">
+      <c r="H28" s="41">
         <f>IF(SUM($V28:$AA28), ROUND(AA28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
@@ -8107,27 +8115,27 @@
         <v>17</v>
       </c>
       <c r="B29" s="26" t="n"/>
-      <c r="C29" s="54">
+      <c r="C29" s="41">
         <f>IF(SUM($V29:$AA29), ROUND(V29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="41">
         <f>IF(SUM($V29:$AA29), ROUND(W29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="E29" s="54">
+      <c r="E29" s="41">
         <f>IF(SUM($V29:$AA29), ROUND(X29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="F29" s="54">
+      <c r="F29" s="41">
         <f>IF(SUM($V29:$AA29), ROUND(Y29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="G29" s="54">
+      <c r="G29" s="41">
         <f>IF(SUM($V29:$AA29), ROUND(Z29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="H29" s="54">
+      <c r="H29" s="41">
         <f>IF(SUM($V29:$AA29), ROUND(AA29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
@@ -8187,27 +8195,27 @@
         <v>18</v>
       </c>
       <c r="B30" s="26" t="n"/>
-      <c r="C30" s="54">
+      <c r="C30" s="41">
         <f>IF(SUM($V30:$AA30), ROUND(V30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="41">
         <f>IF(SUM($V30:$AA30), ROUND(W30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="E30" s="54">
+      <c r="E30" s="41">
         <f>IF(SUM($V30:$AA30), ROUND(X30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="F30" s="54">
+      <c r="F30" s="41">
         <f>IF(SUM($V30:$AA30), ROUND(Y30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="G30" s="54">
+      <c r="G30" s="41">
         <f>IF(SUM($V30:$AA30), ROUND(Z30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="H30" s="54">
+      <c r="H30" s="41">
         <f>IF(SUM($V30:$AA30), ROUND(AA30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
@@ -8267,27 +8275,27 @@
         <v>19</v>
       </c>
       <c r="B31" s="26" t="n"/>
-      <c r="C31" s="54">
+      <c r="C31" s="41">
         <f>IF(SUM($V31:$AA31), ROUND(V31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="D31" s="54">
+      <c r="D31" s="41">
         <f>IF(SUM($V31:$AA31), ROUND(W31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="E31" s="54">
+      <c r="E31" s="41">
         <f>IF(SUM($V31:$AA31), ROUND(X31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="F31" s="54">
+      <c r="F31" s="41">
         <f>IF(SUM($V31:$AA31), ROUND(Y31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="G31" s="54">
+      <c r="G31" s="41">
         <f>IF(SUM($V31:$AA31), ROUND(Z31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="H31" s="54">
+      <c r="H31" s="41">
         <f>IF(SUM($V31:$AA31), ROUND(AA31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
@@ -8347,27 +8355,27 @@
         <v>20</v>
       </c>
       <c r="B32" s="26" t="n"/>
-      <c r="C32" s="54">
+      <c r="C32" s="41">
         <f>IF(SUM($V32:$AA32), ROUND(V32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="41">
         <f>IF(SUM($V32:$AA32), ROUND(W32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="E32" s="54">
+      <c r="E32" s="41">
         <f>IF(SUM($V32:$AA32), ROUND(X32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="F32" s="54">
+      <c r="F32" s="41">
         <f>IF(SUM($V32:$AA32), ROUND(Y32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="G32" s="54">
+      <c r="G32" s="41">
         <f>IF(SUM($V32:$AA32), ROUND(Z32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="H32" s="54">
+      <c r="H32" s="41">
         <f>IF(SUM($V32:$AA32), ROUND(AA32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
@@ -8427,27 +8435,27 @@
         <v>21</v>
       </c>
       <c r="B33" s="26" t="n"/>
-      <c r="C33" s="54">
+      <c r="C33" s="41">
         <f>IF(SUM($V33:$AA33), ROUND(V33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="41">
         <f>IF(SUM($V33:$AA33), ROUND(W33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="E33" s="54">
+      <c r="E33" s="41">
         <f>IF(SUM($V33:$AA33), ROUND(X33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="F33" s="54">
+      <c r="F33" s="41">
         <f>IF(SUM($V33:$AA33), ROUND(Y33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="G33" s="54">
+      <c r="G33" s="41">
         <f>IF(SUM($V33:$AA33), ROUND(Z33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="H33" s="54">
+      <c r="H33" s="41">
         <f>IF(SUM($V33:$AA33), ROUND(AA33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
@@ -8507,27 +8515,27 @@
         <v>22</v>
       </c>
       <c r="B34" s="26" t="n"/>
-      <c r="C34" s="54">
+      <c r="C34" s="41">
         <f>IF(SUM($V34:$AA34), ROUND(V34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="41">
         <f>IF(SUM($V34:$AA34), ROUND(W34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="E34" s="54">
+      <c r="E34" s="41">
         <f>IF(SUM($V34:$AA34), ROUND(X34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="F34" s="54">
+      <c r="F34" s="41">
         <f>IF(SUM($V34:$AA34), ROUND(Y34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="G34" s="54">
+      <c r="G34" s="41">
         <f>IF(SUM($V34:$AA34), ROUND(Z34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="H34" s="54">
+      <c r="H34" s="41">
         <f>IF(SUM($V34:$AA34), ROUND(AA34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
@@ -8587,27 +8595,27 @@
         <v>23</v>
       </c>
       <c r="B35" s="26" t="n"/>
-      <c r="C35" s="54">
+      <c r="C35" s="41">
         <f>IF(SUM($V35:$AA35), ROUND(V35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="D35" s="54">
+      <c r="D35" s="41">
         <f>IF(SUM($V35:$AA35), ROUND(W35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="E35" s="54">
+      <c r="E35" s="41">
         <f>IF(SUM($V35:$AA35), ROUND(X35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="F35" s="54">
+      <c r="F35" s="41">
         <f>IF(SUM($V35:$AA35), ROUND(Y35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="G35" s="54">
+      <c r="G35" s="41">
         <f>IF(SUM($V35:$AA35), ROUND(Z35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="H35" s="54">
+      <c r="H35" s="41">
         <f>IF(SUM($V35:$AA35), ROUND(AA35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
@@ -8667,27 +8675,27 @@
         <v>24</v>
       </c>
       <c r="B36" s="26" t="n"/>
-      <c r="C36" s="54">
+      <c r="C36" s="41">
         <f>IF(SUM($V36:$AA36), ROUND(V36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="D36" s="54">
+      <c r="D36" s="41">
         <f>IF(SUM($V36:$AA36), ROUND(W36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="E36" s="54">
+      <c r="E36" s="41">
         <f>IF(SUM($V36:$AA36), ROUND(X36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="F36" s="54">
+      <c r="F36" s="41">
         <f>IF(SUM($V36:$AA36), ROUND(Y36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="G36" s="54">
+      <c r="G36" s="41">
         <f>IF(SUM($V36:$AA36), ROUND(Z36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="H36" s="54">
+      <c r="H36" s="41">
         <f>IF(SUM($V36:$AA36), ROUND(AA36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
@@ -8747,27 +8755,27 @@
         <v>25</v>
       </c>
       <c r="B37" s="26" t="n"/>
-      <c r="C37" s="54">
+      <c r="C37" s="41">
         <f>IF(SUM($V37:$AA37), ROUND(V37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="D37" s="54">
+      <c r="D37" s="41">
         <f>IF(SUM($V37:$AA37), ROUND(W37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="E37" s="54">
+      <c r="E37" s="41">
         <f>IF(SUM($V37:$AA37), ROUND(X37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="F37" s="54">
+      <c r="F37" s="41">
         <f>IF(SUM($V37:$AA37), ROUND(Y37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="G37" s="54">
+      <c r="G37" s="41">
         <f>IF(SUM($V37:$AA37), ROUND(Z37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="H37" s="54">
+      <c r="H37" s="41">
         <f>IF(SUM($V37:$AA37), ROUND(AA37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
@@ -8827,27 +8835,27 @@
         <v>26</v>
       </c>
       <c r="B38" s="26" t="n"/>
-      <c r="C38" s="54">
+      <c r="C38" s="41">
         <f>IF(SUM($V38:$AA38), ROUND(V38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="D38" s="54">
+      <c r="D38" s="41">
         <f>IF(SUM($V38:$AA38), ROUND(W38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="41">
         <f>IF(SUM($V38:$AA38), ROUND(X38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="F38" s="54">
+      <c r="F38" s="41">
         <f>IF(SUM($V38:$AA38), ROUND(Y38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="G38" s="54">
+      <c r="G38" s="41">
         <f>IF(SUM($V38:$AA38), ROUND(Z38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="H38" s="54">
+      <c r="H38" s="41">
         <f>IF(SUM($V38:$AA38), ROUND(AA38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
@@ -8907,27 +8915,27 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="n"/>
-      <c r="C39" s="54">
+      <c r="C39" s="41">
         <f>IF(SUM($V39:$AA39), ROUND(V39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="D39" s="54">
+      <c r="D39" s="41">
         <f>IF(SUM($V39:$AA39), ROUND(W39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="E39" s="54">
+      <c r="E39" s="41">
         <f>IF(SUM($V39:$AA39), ROUND(X39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="41">
         <f>IF(SUM($V39:$AA39), ROUND(Y39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="41">
         <f>IF(SUM($V39:$AA39), ROUND(Z39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="H39" s="54">
+      <c r="H39" s="41">
         <f>IF(SUM($V39:$AA39), ROUND(AA39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
@@ -8987,27 +8995,27 @@
         <v>28</v>
       </c>
       <c r="B40" s="26" t="n"/>
-      <c r="C40" s="54">
+      <c r="C40" s="41">
         <f>IF(SUM($V40:$AA40), ROUND(V40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="D40" s="54">
+      <c r="D40" s="41">
         <f>IF(SUM($V40:$AA40), ROUND(W40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="E40" s="54">
+      <c r="E40" s="41">
         <f>IF(SUM($V40:$AA40), ROUND(X40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="F40" s="54">
+      <c r="F40" s="41">
         <f>IF(SUM($V40:$AA40), ROUND(Y40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="G40" s="54">
+      <c r="G40" s="41">
         <f>IF(SUM($V40:$AA40), ROUND(Z40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="H40" s="54">
+      <c r="H40" s="41">
         <f>IF(SUM($V40:$AA40), ROUND(AA40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
@@ -9067,27 +9075,27 @@
         <v>29</v>
       </c>
       <c r="B41" s="26" t="n"/>
-      <c r="C41" s="54">
+      <c r="C41" s="41">
         <f>IF(SUM($V41:$AA41), ROUND(V41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="D41" s="54">
+      <c r="D41" s="41">
         <f>IF(SUM($V41:$AA41), ROUND(W41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="E41" s="54">
+      <c r="E41" s="41">
         <f>IF(SUM($V41:$AA41), ROUND(X41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="F41" s="54">
+      <c r="F41" s="41">
         <f>IF(SUM($V41:$AA41), ROUND(Y41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="G41" s="54">
+      <c r="G41" s="41">
         <f>IF(SUM($V41:$AA41), ROUND(Z41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="H41" s="54">
+      <c r="H41" s="41">
         <f>IF(SUM($V41:$AA41), ROUND(AA41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
@@ -9147,27 +9155,27 @@
         <v>30</v>
       </c>
       <c r="B42" s="26" t="n"/>
-      <c r="C42" s="54">
+      <c r="C42" s="41">
         <f>IF(SUM($V42:$AA42), ROUND(V42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="D42" s="54">
+      <c r="D42" s="41">
         <f>IF(SUM($V42:$AA42), ROUND(W42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="E42" s="54">
+      <c r="E42" s="41">
         <f>IF(SUM($V42:$AA42), ROUND(X42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="F42" s="54">
+      <c r="F42" s="41">
         <f>IF(SUM($V42:$AA42), ROUND(Y42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="G42" s="54">
+      <c r="G42" s="41">
         <f>IF(SUM($V42:$AA42), ROUND(Z42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="H42" s="54">
+      <c r="H42" s="41">
         <f>IF(SUM($V42:$AA42), ROUND(AA42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
@@ -9227,27 +9235,27 @@
         <v>31</v>
       </c>
       <c r="B43" s="26" t="n"/>
-      <c r="C43" s="54">
+      <c r="C43" s="41">
         <f>IF(SUM($V43:$AA43), ROUND(V43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="D43" s="54">
+      <c r="D43" s="41">
         <f>IF(SUM($V43:$AA43), ROUND(W43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="E43" s="54">
+      <c r="E43" s="41">
         <f>IF(SUM($V43:$AA43), ROUND(X43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="41">
         <f>IF(SUM($V43:$AA43), ROUND(Y43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="41">
         <f>IF(SUM($V43:$AA43), ROUND(Z43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="H43" s="54">
+      <c r="H43" s="41">
         <f>IF(SUM($V43:$AA43), ROUND(AA43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
@@ -9307,27 +9315,27 @@
         <v>32</v>
       </c>
       <c r="B44" s="26" t="n"/>
-      <c r="C44" s="54">
+      <c r="C44" s="41">
         <f>IF(SUM($V44:$AA44), ROUND(V44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="D44" s="54">
+      <c r="D44" s="41">
         <f>IF(SUM($V44:$AA44), ROUND(W44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="E44" s="54">
+      <c r="E44" s="41">
         <f>IF(SUM($V44:$AA44), ROUND(X44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="F44" s="54">
+      <c r="F44" s="41">
         <f>IF(SUM($V44:$AA44), ROUND(Y44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="G44" s="54">
+      <c r="G44" s="41">
         <f>IF(SUM($V44:$AA44), ROUND(Z44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="H44" s="54">
+      <c r="H44" s="41">
         <f>IF(SUM($V44:$AA44), ROUND(AA44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
@@ -9387,27 +9395,27 @@
         <v>33</v>
       </c>
       <c r="B45" s="26" t="n"/>
-      <c r="C45" s="54">
+      <c r="C45" s="41">
         <f>IF(SUM($V45:$AA45), ROUND(V45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="D45" s="54">
+      <c r="D45" s="41">
         <f>IF(SUM($V45:$AA45), ROUND(W45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="E45" s="54">
+      <c r="E45" s="41">
         <f>IF(SUM($V45:$AA45), ROUND(X45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="41">
         <f>IF(SUM($V45:$AA45), ROUND(Y45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="G45" s="54">
+      <c r="G45" s="41">
         <f>IF(SUM($V45:$AA45), ROUND(Z45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="H45" s="54">
+      <c r="H45" s="41">
         <f>IF(SUM($V45:$AA45), ROUND(AA45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
@@ -9467,27 +9475,27 @@
         <v>34</v>
       </c>
       <c r="B46" s="26" t="n"/>
-      <c r="C46" s="54">
+      <c r="C46" s="41">
         <f>IF(SUM($V46:$AA46), ROUND(V46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="D46" s="54">
+      <c r="D46" s="41">
         <f>IF(SUM($V46:$AA46), ROUND(W46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="E46" s="54">
+      <c r="E46" s="41">
         <f>IF(SUM($V46:$AA46), ROUND(X46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="F46" s="54">
+      <c r="F46" s="41">
         <f>IF(SUM($V46:$AA46), ROUND(Y46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="G46" s="54">
+      <c r="G46" s="41">
         <f>IF(SUM($V46:$AA46), ROUND(Z46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="H46" s="54">
+      <c r="H46" s="41">
         <f>IF(SUM($V46:$AA46), ROUND(AA46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
@@ -9547,27 +9555,27 @@
         <v>35</v>
       </c>
       <c r="B47" s="26" t="n"/>
-      <c r="C47" s="54">
+      <c r="C47" s="41">
         <f>IF(SUM($V47:$AA47), ROUND(V47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="D47" s="54">
+      <c r="D47" s="41">
         <f>IF(SUM($V47:$AA47), ROUND(W47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="E47" s="54">
+      <c r="E47" s="41">
         <f>IF(SUM($V47:$AA47), ROUND(X47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="F47" s="54">
+      <c r="F47" s="41">
         <f>IF(SUM($V47:$AA47), ROUND(Y47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="G47" s="54">
+      <c r="G47" s="41">
         <f>IF(SUM($V47:$AA47), ROUND(Z47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="H47" s="54">
+      <c r="H47" s="41">
         <f>IF(SUM($V47:$AA47), ROUND(AA47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
@@ -9627,27 +9635,27 @@
         <v>36</v>
       </c>
       <c r="B48" s="26" t="n"/>
-      <c r="C48" s="54">
+      <c r="C48" s="41">
         <f>IF(SUM($V48:$AA48), ROUND(V48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="41">
         <f>IF(SUM($V48:$AA48), ROUND(W48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="E48" s="54">
+      <c r="E48" s="41">
         <f>IF(SUM($V48:$AA48), ROUND(X48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="F48" s="54">
+      <c r="F48" s="41">
         <f>IF(SUM($V48:$AA48), ROUND(Y48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="G48" s="54">
+      <c r="G48" s="41">
         <f>IF(SUM($V48:$AA48), ROUND(Z48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="H48" s="54">
+      <c r="H48" s="41">
         <f>IF(SUM($V48:$AA48), ROUND(AA48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
@@ -9707,27 +9715,27 @@
         <v>37</v>
       </c>
       <c r="B49" s="26" t="n"/>
-      <c r="C49" s="54">
+      <c r="C49" s="41">
         <f>IF(SUM($V49:$AA49), ROUND(V49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="D49" s="54">
+      <c r="D49" s="41">
         <f>IF(SUM($V49:$AA49), ROUND(W49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="E49" s="54">
+      <c r="E49" s="41">
         <f>IF(SUM($V49:$AA49), ROUND(X49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="F49" s="54">
+      <c r="F49" s="41">
         <f>IF(SUM($V49:$AA49), ROUND(Y49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="G49" s="54">
+      <c r="G49" s="41">
         <f>IF(SUM($V49:$AA49), ROUND(Z49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="H49" s="54">
+      <c r="H49" s="41">
         <f>IF(SUM($V49:$AA49), ROUND(AA49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
@@ -9787,27 +9795,27 @@
         <v>38</v>
       </c>
       <c r="B50" s="26" t="n"/>
-      <c r="C50" s="54">
+      <c r="C50" s="41">
         <f>IF(SUM($V50:$AA50), ROUND(V50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="D50" s="54">
+      <c r="D50" s="41">
         <f>IF(SUM($V50:$AA50), ROUND(W50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="E50" s="54">
+      <c r="E50" s="41">
         <f>IF(SUM($V50:$AA50), ROUND(X50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="F50" s="54">
+      <c r="F50" s="41">
         <f>IF(SUM($V50:$AA50), ROUND(Y50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="G50" s="54">
+      <c r="G50" s="41">
         <f>IF(SUM($V50:$AA50), ROUND(Z50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="H50" s="54">
+      <c r="H50" s="41">
         <f>IF(SUM($V50:$AA50), ROUND(AA50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
@@ -9867,27 +9875,27 @@
         <v>39</v>
       </c>
       <c r="B51" s="26" t="n"/>
-      <c r="C51" s="54">
+      <c r="C51" s="41">
         <f>IF(SUM($V51:$AA51), ROUND(V51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="D51" s="54">
+      <c r="D51" s="41">
         <f>IF(SUM($V51:$AA51), ROUND(W51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="E51" s="54">
+      <c r="E51" s="41">
         <f>IF(SUM($V51:$AA51), ROUND(X51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="F51" s="54">
+      <c r="F51" s="41">
         <f>IF(SUM($V51:$AA51), ROUND(Y51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="G51" s="54">
+      <c r="G51" s="41">
         <f>IF(SUM($V51:$AA51), ROUND(Z51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="H51" s="54">
+      <c r="H51" s="41">
         <f>IF(SUM($V51:$AA51), ROUND(AA51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
@@ -9947,27 +9955,27 @@
         <v>40</v>
       </c>
       <c r="B52" s="26" t="n"/>
-      <c r="C52" s="54">
+      <c r="C52" s="41">
         <f>IF(SUM($V52:$AA52), ROUND(V52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="D52" s="54">
+      <c r="D52" s="41">
         <f>IF(SUM($V52:$AA52), ROUND(W52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="E52" s="54">
+      <c r="E52" s="41">
         <f>IF(SUM($V52:$AA52), ROUND(X52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="F52" s="54">
+      <c r="F52" s="41">
         <f>IF(SUM($V52:$AA52), ROUND(Y52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="G52" s="54">
+      <c r="G52" s="41">
         <f>IF(SUM($V52:$AA52), ROUND(Z52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="H52" s="54">
+      <c r="H52" s="41">
         <f>IF(SUM($V52:$AA52), ROUND(AA52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
@@ -10027,27 +10035,27 @@
         <v>41</v>
       </c>
       <c r="B53" s="26" t="n"/>
-      <c r="C53" s="54">
+      <c r="C53" s="41">
         <f>IF(SUM($V53:$AA53), ROUND(V53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="D53" s="54">
+      <c r="D53" s="41">
         <f>IF(SUM($V53:$AA53), ROUND(W53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="E53" s="54">
+      <c r="E53" s="41">
         <f>IF(SUM($V53:$AA53), ROUND(X53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="F53" s="54">
+      <c r="F53" s="41">
         <f>IF(SUM($V53:$AA53), ROUND(Y53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="G53" s="54">
+      <c r="G53" s="41">
         <f>IF(SUM($V53:$AA53), ROUND(Z53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="H53" s="54">
+      <c r="H53" s="41">
         <f>IF(SUM($V53:$AA53), ROUND(AA53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
@@ -10107,27 +10115,27 @@
         <v>42</v>
       </c>
       <c r="B54" s="26" t="n"/>
-      <c r="C54" s="54">
+      <c r="C54" s="41">
         <f>IF(SUM($V54:$AA54), ROUND(V54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="D54" s="54">
+      <c r="D54" s="41">
         <f>IF(SUM($V54:$AA54), ROUND(W54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="E54" s="54">
+      <c r="E54" s="41">
         <f>IF(SUM($V54:$AA54), ROUND(X54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="F54" s="54">
+      <c r="F54" s="41">
         <f>IF(SUM($V54:$AA54), ROUND(Y54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="G54" s="54">
+      <c r="G54" s="41">
         <f>IF(SUM($V54:$AA54), ROUND(Z54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="H54" s="54">
+      <c r="H54" s="41">
         <f>IF(SUM($V54:$AA54), ROUND(AA54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
@@ -10187,27 +10195,27 @@
         <v>43</v>
       </c>
       <c r="B55" s="26" t="n"/>
-      <c r="C55" s="54">
+      <c r="C55" s="41">
         <f>IF(SUM($V55:$AA55), ROUND(V55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="D55" s="54">
+      <c r="D55" s="41">
         <f>IF(SUM($V55:$AA55), ROUND(W55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="E55" s="54">
+      <c r="E55" s="41">
         <f>IF(SUM($V55:$AA55), ROUND(X55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="F55" s="54">
+      <c r="F55" s="41">
         <f>IF(SUM($V55:$AA55), ROUND(Y55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="G55" s="54">
+      <c r="G55" s="41">
         <f>IF(SUM($V55:$AA55), ROUND(Z55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="H55" s="54">
+      <c r="H55" s="41">
         <f>IF(SUM($V55:$AA55), ROUND(AA55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
@@ -10267,27 +10275,27 @@
         <v>44</v>
       </c>
       <c r="B56" s="26" t="n"/>
-      <c r="C56" s="54">
+      <c r="C56" s="41">
         <f>IF(SUM($V56:$AA56), ROUND(V56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="D56" s="54">
+      <c r="D56" s="41">
         <f>IF(SUM($V56:$AA56), ROUND(W56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="E56" s="54">
+      <c r="E56" s="41">
         <f>IF(SUM($V56:$AA56), ROUND(X56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="F56" s="54">
+      <c r="F56" s="41">
         <f>IF(SUM($V56:$AA56), ROUND(Y56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="G56" s="54">
+      <c r="G56" s="41">
         <f>IF(SUM($V56:$AA56), ROUND(Z56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="H56" s="54">
+      <c r="H56" s="41">
         <f>IF(SUM($V56:$AA56), ROUND(AA56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
@@ -10347,27 +10355,27 @@
         <v>45</v>
       </c>
       <c r="B57" s="26" t="n"/>
-      <c r="C57" s="54">
+      <c r="C57" s="41">
         <f>IF(SUM($V57:$AA57), ROUND(V57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="D57" s="54">
+      <c r="D57" s="41">
         <f>IF(SUM($V57:$AA57), ROUND(W57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="E57" s="54">
+      <c r="E57" s="41">
         <f>IF(SUM($V57:$AA57), ROUND(X57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="F57" s="54">
+      <c r="F57" s="41">
         <f>IF(SUM($V57:$AA57), ROUND(Y57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="G57" s="54">
+      <c r="G57" s="41">
         <f>IF(SUM($V57:$AA57), ROUND(Z57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="H57" s="54">
+      <c r="H57" s="41">
         <f>IF(SUM($V57:$AA57), ROUND(AA57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
@@ -10427,27 +10435,27 @@
         <v>46</v>
       </c>
       <c r="B58" s="26" t="n"/>
-      <c r="C58" s="54">
+      <c r="C58" s="41">
         <f>IF(SUM($V58:$AA58), ROUND(V58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="D58" s="54">
+      <c r="D58" s="41">
         <f>IF(SUM($V58:$AA58), ROUND(W58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="E58" s="54">
+      <c r="E58" s="41">
         <f>IF(SUM($V58:$AA58), ROUND(X58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="F58" s="54">
+      <c r="F58" s="41">
         <f>IF(SUM($V58:$AA58), ROUND(Y58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="G58" s="54">
+      <c r="G58" s="41">
         <f>IF(SUM($V58:$AA58), ROUND(Z58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="H58" s="54">
+      <c r="H58" s="41">
         <f>IF(SUM($V58:$AA58), ROUND(AA58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
@@ -10507,27 +10515,27 @@
         <v>47</v>
       </c>
       <c r="B59" s="26" t="n"/>
-      <c r="C59" s="54">
+      <c r="C59" s="41">
         <f>IF(SUM($V59:$AA59), ROUND(V59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="D59" s="54">
+      <c r="D59" s="41">
         <f>IF(SUM($V59:$AA59), ROUND(W59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="E59" s="54">
+      <c r="E59" s="41">
         <f>IF(SUM($V59:$AA59), ROUND(X59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="F59" s="54">
+      <c r="F59" s="41">
         <f>IF(SUM($V59:$AA59), ROUND(Y59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="G59" s="54">
+      <c r="G59" s="41">
         <f>IF(SUM($V59:$AA59), ROUND(Z59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="H59" s="54">
+      <c r="H59" s="41">
         <f>IF(SUM($V59:$AA59), ROUND(AA59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
@@ -10587,27 +10595,27 @@
         <v>48</v>
       </c>
       <c r="B60" s="26" t="n"/>
-      <c r="C60" s="54">
+      <c r="C60" s="41">
         <f>IF(SUM($V60:$AA60), ROUND(V60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="D60" s="54">
+      <c r="D60" s="41">
         <f>IF(SUM($V60:$AA60), ROUND(W60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="E60" s="54">
+      <c r="E60" s="41">
         <f>IF(SUM($V60:$AA60), ROUND(X60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="F60" s="54">
+      <c r="F60" s="41">
         <f>IF(SUM($V60:$AA60), ROUND(Y60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="G60" s="54">
+      <c r="G60" s="41">
         <f>IF(SUM($V60:$AA60), ROUND(Z60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="H60" s="54">
+      <c r="H60" s="41">
         <f>IF(SUM($V60:$AA60), ROUND(AA60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
@@ -10667,27 +10675,27 @@
         <v>49</v>
       </c>
       <c r="B61" s="26" t="n"/>
-      <c r="C61" s="54">
+      <c r="C61" s="41">
         <f>IF(SUM($V61:$AA61), ROUND(V61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="D61" s="54">
+      <c r="D61" s="41">
         <f>IF(SUM($V61:$AA61), ROUND(W61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="E61" s="54">
+      <c r="E61" s="41">
         <f>IF(SUM($V61:$AA61), ROUND(X61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="F61" s="54">
+      <c r="F61" s="41">
         <f>IF(SUM($V61:$AA61), ROUND(Y61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="G61" s="54">
+      <c r="G61" s="41">
         <f>IF(SUM($V61:$AA61), ROUND(Z61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="H61" s="54">
+      <c r="H61" s="41">
         <f>IF(SUM($V61:$AA61), ROUND(AA61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
@@ -10747,27 +10755,27 @@
         <v>50</v>
       </c>
       <c r="B62" s="26" t="n"/>
-      <c r="C62" s="54">
+      <c r="C62" s="41">
         <f>IF(SUM($V62:$AA62), ROUND(V62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="D62" s="54">
+      <c r="D62" s="41">
         <f>IF(SUM($V62:$AA62), ROUND(W62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="E62" s="54">
+      <c r="E62" s="41">
         <f>IF(SUM($V62:$AA62), ROUND(X62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="F62" s="54">
+      <c r="F62" s="41">
         <f>IF(SUM($V62:$AA62), ROUND(Y62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="G62" s="54">
+      <c r="G62" s="41">
         <f>IF(SUM($V62:$AA62), ROUND(Z62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="H62" s="54">
+      <c r="H62" s="41">
         <f>IF(SUM($V62:$AA62), ROUND(AA62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
@@ -10827,27 +10835,27 @@
         <v>51</v>
       </c>
       <c r="B63" s="26" t="n"/>
-      <c r="C63" s="54">
+      <c r="C63" s="41">
         <f>IF(SUM($V63:$AA63), ROUND(V63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="D63" s="54">
+      <c r="D63" s="41">
         <f>IF(SUM($V63:$AA63), ROUND(W63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="E63" s="54">
+      <c r="E63" s="41">
         <f>IF(SUM($V63:$AA63), ROUND(X63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="F63" s="54">
+      <c r="F63" s="41">
         <f>IF(SUM($V63:$AA63), ROUND(Y63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="G63" s="54">
+      <c r="G63" s="41">
         <f>IF(SUM($V63:$AA63), ROUND(Z63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="H63" s="54">
+      <c r="H63" s="41">
         <f>IF(SUM($V63:$AA63), ROUND(AA63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
@@ -10907,27 +10915,27 @@
         <v>52</v>
       </c>
       <c r="B64" s="26" t="n"/>
-      <c r="C64" s="54">
+      <c r="C64" s="41">
         <f>IF(SUM($V64:$AA64), ROUND(V64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="D64" s="54">
+      <c r="D64" s="41">
         <f>IF(SUM($V64:$AA64), ROUND(W64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="E64" s="54">
+      <c r="E64" s="41">
         <f>IF(SUM($V64:$AA64), ROUND(X64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="F64" s="54">
+      <c r="F64" s="41">
         <f>IF(SUM($V64:$AA64), ROUND(Y64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="G64" s="54">
+      <c r="G64" s="41">
         <f>IF(SUM($V64:$AA64), ROUND(Z64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="H64" s="54">
+      <c r="H64" s="41">
         <f>IF(SUM($V64:$AA64), ROUND(AA64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
@@ -10987,27 +10995,27 @@
         <v>53</v>
       </c>
       <c r="B65" s="26" t="n"/>
-      <c r="C65" s="54">
+      <c r="C65" s="41">
         <f>IF(SUM($V65:$AA65), ROUND(V65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="D65" s="54">
+      <c r="D65" s="41">
         <f>IF(SUM($V65:$AA65), ROUND(W65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="E65" s="54">
+      <c r="E65" s="41">
         <f>IF(SUM($V65:$AA65), ROUND(X65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="F65" s="54">
+      <c r="F65" s="41">
         <f>IF(SUM($V65:$AA65), ROUND(Y65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="G65" s="54">
+      <c r="G65" s="41">
         <f>IF(SUM($V65:$AA65), ROUND(Z65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="H65" s="54">
+      <c r="H65" s="41">
         <f>IF(SUM($V65:$AA65), ROUND(AA65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
@@ -11067,27 +11075,27 @@
         <v>54</v>
       </c>
       <c r="B66" s="26" t="n"/>
-      <c r="C66" s="54">
+      <c r="C66" s="41">
         <f>IF(SUM($V66:$AA66), ROUND(V66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="D66" s="54">
+      <c r="D66" s="41">
         <f>IF(SUM($V66:$AA66), ROUND(W66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="E66" s="54">
+      <c r="E66" s="41">
         <f>IF(SUM($V66:$AA66), ROUND(X66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="F66" s="54">
+      <c r="F66" s="41">
         <f>IF(SUM($V66:$AA66), ROUND(Y66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="G66" s="54">
+      <c r="G66" s="41">
         <f>IF(SUM($V66:$AA66), ROUND(Z66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="H66" s="54">
+      <c r="H66" s="41">
         <f>IF(SUM($V66:$AA66), ROUND(AA66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
@@ -11147,27 +11155,27 @@
         <v>55</v>
       </c>
       <c r="B67" s="26" t="n"/>
-      <c r="C67" s="54">
+      <c r="C67" s="41">
         <f>IF(SUM($V67:$AA67), ROUND(V67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="D67" s="54">
+      <c r="D67" s="41">
         <f>IF(SUM($V67:$AA67), ROUND(W67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="E67" s="54">
+      <c r="E67" s="41">
         <f>IF(SUM($V67:$AA67), ROUND(X67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="F67" s="54">
+      <c r="F67" s="41">
         <f>IF(SUM($V67:$AA67), ROUND(Y67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="G67" s="54">
+      <c r="G67" s="41">
         <f>IF(SUM($V67:$AA67), ROUND(Z67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="H67" s="54">
+      <c r="H67" s="41">
         <f>IF(SUM($V67:$AA67), ROUND(AA67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
@@ -11227,27 +11235,27 @@
         <v>56</v>
       </c>
       <c r="B68" s="26" t="n"/>
-      <c r="C68" s="54">
+      <c r="C68" s="41">
         <f>IF(SUM($V68:$AA68), ROUND(V68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="D68" s="54">
+      <c r="D68" s="41">
         <f>IF(SUM($V68:$AA68), ROUND(W68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="E68" s="54">
+      <c r="E68" s="41">
         <f>IF(SUM($V68:$AA68), ROUND(X68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="F68" s="54">
+      <c r="F68" s="41">
         <f>IF(SUM($V68:$AA68), ROUND(Y68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="G68" s="54">
+      <c r="G68" s="41">
         <f>IF(SUM($V68:$AA68), ROUND(Z68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="H68" s="54">
+      <c r="H68" s="41">
         <f>IF(SUM($V68:$AA68), ROUND(AA68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
@@ -11307,27 +11315,27 @@
         <v>57</v>
       </c>
       <c r="B69" s="26" t="n"/>
-      <c r="C69" s="54">
+      <c r="C69" s="41">
         <f>IF(SUM($V69:$AA69), ROUND(V69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="D69" s="54">
+      <c r="D69" s="41">
         <f>IF(SUM($V69:$AA69), ROUND(W69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="E69" s="54">
+      <c r="E69" s="41">
         <f>IF(SUM($V69:$AA69), ROUND(X69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="F69" s="54">
+      <c r="F69" s="41">
         <f>IF(SUM($V69:$AA69), ROUND(Y69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="G69" s="54">
+      <c r="G69" s="41">
         <f>IF(SUM($V69:$AA69), ROUND(Z69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="H69" s="54">
+      <c r="H69" s="41">
         <f>IF(SUM($V69:$AA69), ROUND(AA69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
@@ -11387,27 +11395,27 @@
         <v>58</v>
       </c>
       <c r="B70" s="26" t="n"/>
-      <c r="C70" s="54">
+      <c r="C70" s="41">
         <f>IF(SUM($V70:$AA70), ROUND(V70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="D70" s="54">
+      <c r="D70" s="41">
         <f>IF(SUM($V70:$AA70), ROUND(W70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="E70" s="54">
+      <c r="E70" s="41">
         <f>IF(SUM($V70:$AA70), ROUND(X70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="F70" s="54">
+      <c r="F70" s="41">
         <f>IF(SUM($V70:$AA70), ROUND(Y70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="G70" s="54">
+      <c r="G70" s="41">
         <f>IF(SUM($V70:$AA70), ROUND(Z70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="H70" s="54">
+      <c r="H70" s="41">
         <f>IF(SUM($V70:$AA70), ROUND(AA70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
@@ -11467,27 +11475,27 @@
         <v>59</v>
       </c>
       <c r="B71" s="26" t="n"/>
-      <c r="C71" s="54">
+      <c r="C71" s="41">
         <f>IF(SUM($V71:$AA71), ROUND(V71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="D71" s="54">
+      <c r="D71" s="41">
         <f>IF(SUM($V71:$AA71), ROUND(W71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="E71" s="54">
+      <c r="E71" s="41">
         <f>IF(SUM($V71:$AA71), ROUND(X71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="F71" s="54">
+      <c r="F71" s="41">
         <f>IF(SUM($V71:$AA71), ROUND(Y71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="G71" s="54">
+      <c r="G71" s="41">
         <f>IF(SUM($V71:$AA71), ROUND(Z71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="H71" s="54">
+      <c r="H71" s="41">
         <f>IF(SUM($V71:$AA71), ROUND(AA71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
@@ -11547,27 +11555,27 @@
         <v>60</v>
       </c>
       <c r="B72" s="26" t="n"/>
-      <c r="C72" s="54">
+      <c r="C72" s="41">
         <f>IF(SUM($V72:$AA72), ROUND(V72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="D72" s="54">
+      <c r="D72" s="41">
         <f>IF(SUM($V72:$AA72), ROUND(W72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="E72" s="54">
+      <c r="E72" s="41">
         <f>IF(SUM($V72:$AA72), ROUND(X72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="F72" s="54">
+      <c r="F72" s="41">
         <f>IF(SUM($V72:$AA72), ROUND(Y72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="G72" s="54">
+      <c r="G72" s="41">
         <f>IF(SUM($V72:$AA72), ROUND(Z72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="H72" s="54">
+      <c r="H72" s="41">
         <f>IF(SUM($V72:$AA72), ROUND(AA72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
@@ -11627,27 +11635,27 @@
         <v>61</v>
       </c>
       <c r="B73" s="26" t="n"/>
-      <c r="C73" s="54">
+      <c r="C73" s="41">
         <f>IF(SUM($V73:$AA73), ROUND(V73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="D73" s="54">
+      <c r="D73" s="41">
         <f>IF(SUM($V73:$AA73), ROUND(W73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="E73" s="54">
+      <c r="E73" s="41">
         <f>IF(SUM($V73:$AA73), ROUND(X73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="F73" s="54">
+      <c r="F73" s="41">
         <f>IF(SUM($V73:$AA73), ROUND(Y73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="G73" s="54">
+      <c r="G73" s="41">
         <f>IF(SUM($V73:$AA73), ROUND(Z73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="H73" s="54">
+      <c r="H73" s="41">
         <f>IF(SUM($V73:$AA73), ROUND(AA73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
@@ -11707,27 +11715,27 @@
         <v>62</v>
       </c>
       <c r="B74" s="26" t="n"/>
-      <c r="C74" s="54">
+      <c r="C74" s="41">
         <f>IF(SUM($V74:$AA74), ROUND(V74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="D74" s="54">
+      <c r="D74" s="41">
         <f>IF(SUM($V74:$AA74), ROUND(W74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="E74" s="54">
+      <c r="E74" s="41">
         <f>IF(SUM($V74:$AA74), ROUND(X74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="F74" s="54">
+      <c r="F74" s="41">
         <f>IF(SUM($V74:$AA74), ROUND(Y74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="G74" s="54">
+      <c r="G74" s="41">
         <f>IF(SUM($V74:$AA74), ROUND(Z74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="H74" s="54">
+      <c r="H74" s="41">
         <f>IF(SUM($V74:$AA74), ROUND(AA74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
@@ -11787,27 +11795,27 @@
         <v>63</v>
       </c>
       <c r="B75" s="26" t="n"/>
-      <c r="C75" s="54">
+      <c r="C75" s="41">
         <f>IF(SUM($V75:$AA75), ROUND(V75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="D75" s="54">
+      <c r="D75" s="41">
         <f>IF(SUM($V75:$AA75), ROUND(W75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="E75" s="54">
+      <c r="E75" s="41">
         <f>IF(SUM($V75:$AA75), ROUND(X75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="F75" s="54">
+      <c r="F75" s="41">
         <f>IF(SUM($V75:$AA75), ROUND(Y75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="G75" s="54">
+      <c r="G75" s="41">
         <f>IF(SUM($V75:$AA75), ROUND(Z75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="H75" s="54">
+      <c r="H75" s="41">
         <f>IF(SUM($V75:$AA75), ROUND(AA75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
@@ -11867,27 +11875,27 @@
         <v>64</v>
       </c>
       <c r="B76" s="26" t="n"/>
-      <c r="C76" s="54">
+      <c r="C76" s="41">
         <f>IF(SUM($V76:$AA76), ROUND(V76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="D76" s="54">
+      <c r="D76" s="41">
         <f>IF(SUM($V76:$AA76), ROUND(W76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="E76" s="54">
+      <c r="E76" s="41">
         <f>IF(SUM($V76:$AA76), ROUND(X76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="F76" s="54">
+      <c r="F76" s="41">
         <f>IF(SUM($V76:$AA76), ROUND(Y76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="G76" s="54">
+      <c r="G76" s="41">
         <f>IF(SUM($V76:$AA76), ROUND(Z76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="H76" s="54">
+      <c r="H76" s="41">
         <f>IF(SUM($V76:$AA76), ROUND(AA76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
@@ -11947,27 +11955,27 @@
         <v>65</v>
       </c>
       <c r="B77" s="26" t="n"/>
-      <c r="C77" s="54">
+      <c r="C77" s="41">
         <f>IF(SUM($V77:$AA77), ROUND(V77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="D77" s="54">
+      <c r="D77" s="41">
         <f>IF(SUM($V77:$AA77), ROUND(W77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="E77" s="54">
+      <c r="E77" s="41">
         <f>IF(SUM($V77:$AA77), ROUND(X77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="F77" s="54">
+      <c r="F77" s="41">
         <f>IF(SUM($V77:$AA77), ROUND(Y77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="G77" s="54">
+      <c r="G77" s="41">
         <f>IF(SUM($V77:$AA77), ROUND(Z77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="H77" s="54">
+      <c r="H77" s="41">
         <f>IF(SUM($V77:$AA77), ROUND(AA77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
@@ -12027,27 +12035,27 @@
         <v>66</v>
       </c>
       <c r="B78" s="26" t="n"/>
-      <c r="C78" s="54">
+      <c r="C78" s="41">
         <f>IF(SUM($V78:$AA78), ROUND(V78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="D78" s="54">
+      <c r="D78" s="41">
         <f>IF(SUM($V78:$AA78), ROUND(W78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="E78" s="54">
+      <c r="E78" s="41">
         <f>IF(SUM($V78:$AA78), ROUND(X78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="F78" s="54">
+      <c r="F78" s="41">
         <f>IF(SUM($V78:$AA78), ROUND(Y78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="G78" s="54">
+      <c r="G78" s="41">
         <f>IF(SUM($V78:$AA78), ROUND(Z78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="H78" s="54">
+      <c r="H78" s="41">
         <f>IF(SUM($V78:$AA78), ROUND(AA78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
@@ -12107,27 +12115,27 @@
         <v>67</v>
       </c>
       <c r="B79" s="26" t="n"/>
-      <c r="C79" s="54">
+      <c r="C79" s="41">
         <f>IF(SUM($V79:$AA79), ROUND(V79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="D79" s="54">
+      <c r="D79" s="41">
         <f>IF(SUM($V79:$AA79), ROUND(W79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="E79" s="54">
+      <c r="E79" s="41">
         <f>IF(SUM($V79:$AA79), ROUND(X79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="F79" s="54">
+      <c r="F79" s="41">
         <f>IF(SUM($V79:$AA79), ROUND(Y79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="G79" s="54">
+      <c r="G79" s="41">
         <f>IF(SUM($V79:$AA79), ROUND(Z79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="H79" s="54">
+      <c r="H79" s="41">
         <f>IF(SUM($V79:$AA79), ROUND(AA79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
@@ -12187,27 +12195,27 @@
         <v>68</v>
       </c>
       <c r="B80" s="26" t="n"/>
-      <c r="C80" s="54">
+      <c r="C80" s="41">
         <f>IF(SUM($V80:$AA80), ROUND(V80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="D80" s="54">
+      <c r="D80" s="41">
         <f>IF(SUM($V80:$AA80), ROUND(W80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="E80" s="54">
+      <c r="E80" s="41">
         <f>IF(SUM($V80:$AA80), ROUND(X80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="F80" s="54">
+      <c r="F80" s="41">
         <f>IF(SUM($V80:$AA80), ROUND(Y80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="G80" s="54">
+      <c r="G80" s="41">
         <f>IF(SUM($V80:$AA80), ROUND(Z80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="H80" s="54">
+      <c r="H80" s="41">
         <f>IF(SUM($V80:$AA80), ROUND(AA80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
@@ -12267,27 +12275,27 @@
         <v>69</v>
       </c>
       <c r="B81" s="26" t="n"/>
-      <c r="C81" s="54">
+      <c r="C81" s="41">
         <f>IF(SUM($V81:$AA81), ROUND(V81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="D81" s="54">
+      <c r="D81" s="41">
         <f>IF(SUM($V81:$AA81), ROUND(W81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="E81" s="54">
+      <c r="E81" s="41">
         <f>IF(SUM($V81:$AA81), ROUND(X81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="F81" s="54">
+      <c r="F81" s="41">
         <f>IF(SUM($V81:$AA81), ROUND(Y81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="G81" s="54">
+      <c r="G81" s="41">
         <f>IF(SUM($V81:$AA81), ROUND(Z81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="H81" s="54">
+      <c r="H81" s="41">
         <f>IF(SUM($V81:$AA81), ROUND(AA81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
@@ -12347,27 +12355,27 @@
         <v>70</v>
       </c>
       <c r="B82" s="26" t="n"/>
-      <c r="C82" s="54">
+      <c r="C82" s="41">
         <f>IF(SUM($V82:$AA82), ROUND(V82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="D82" s="54">
+      <c r="D82" s="41">
         <f>IF(SUM($V82:$AA82), ROUND(W82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="E82" s="54">
+      <c r="E82" s="41">
         <f>IF(SUM($V82:$AA82), ROUND(X82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="F82" s="54">
+      <c r="F82" s="41">
         <f>IF(SUM($V82:$AA82), ROUND(Y82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="G82" s="54">
+      <c r="G82" s="41">
         <f>IF(SUM($V82:$AA82), ROUND(Z82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="H82" s="54">
+      <c r="H82" s="41">
         <f>IF(SUM($V82:$AA82), ROUND(AA82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
@@ -12427,27 +12435,27 @@
         <v>71</v>
       </c>
       <c r="B83" s="26" t="n"/>
-      <c r="C83" s="54">
+      <c r="C83" s="41">
         <f>IF(SUM($V83:$AA83), ROUND(V83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="D83" s="54">
+      <c r="D83" s="41">
         <f>IF(SUM($V83:$AA83), ROUND(W83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="E83" s="54">
+      <c r="E83" s="41">
         <f>IF(SUM($V83:$AA83), ROUND(X83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="F83" s="54">
+      <c r="F83" s="41">
         <f>IF(SUM($V83:$AA83), ROUND(Y83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="G83" s="54">
+      <c r="G83" s="41">
         <f>IF(SUM($V83:$AA83), ROUND(Z83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="H83" s="54">
+      <c r="H83" s="41">
         <f>IF(SUM($V83:$AA83), ROUND(AA83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
@@ -12507,27 +12515,27 @@
         <v>72</v>
       </c>
       <c r="B84" s="26" t="n"/>
-      <c r="C84" s="54">
+      <c r="C84" s="41">
         <f>IF(SUM($V84:$AA84), ROUND(V84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="D84" s="54">
+      <c r="D84" s="41">
         <f>IF(SUM($V84:$AA84), ROUND(W84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="E84" s="54">
+      <c r="E84" s="41">
         <f>IF(SUM($V84:$AA84), ROUND(X84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="F84" s="54">
+      <c r="F84" s="41">
         <f>IF(SUM($V84:$AA84), ROUND(Y84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="G84" s="54">
+      <c r="G84" s="41">
         <f>IF(SUM($V84:$AA84), ROUND(Z84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="H84" s="54">
+      <c r="H84" s="41">
         <f>IF(SUM($V84:$AA84), ROUND(AA84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
@@ -12587,27 +12595,27 @@
         <v>73</v>
       </c>
       <c r="B85" s="26" t="n"/>
-      <c r="C85" s="54">
+      <c r="C85" s="41">
         <f>IF(SUM($V85:$AA85), ROUND(V85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="D85" s="54">
+      <c r="D85" s="41">
         <f>IF(SUM($V85:$AA85), ROUND(W85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="E85" s="54">
+      <c r="E85" s="41">
         <f>IF(SUM($V85:$AA85), ROUND(X85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="F85" s="54">
+      <c r="F85" s="41">
         <f>IF(SUM($V85:$AA85), ROUND(Y85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="G85" s="54">
+      <c r="G85" s="41">
         <f>IF(SUM($V85:$AA85), ROUND(Z85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="H85" s="54">
+      <c r="H85" s="41">
         <f>IF(SUM($V85:$AA85), ROUND(AA85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
@@ -12667,27 +12675,27 @@
         <v>74</v>
       </c>
       <c r="B86" s="26" t="n"/>
-      <c r="C86" s="54">
+      <c r="C86" s="41">
         <f>IF(SUM($V86:$AA86), ROUND(V86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="D86" s="54">
+      <c r="D86" s="41">
         <f>IF(SUM($V86:$AA86), ROUND(W86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="E86" s="54">
+      <c r="E86" s="41">
         <f>IF(SUM($V86:$AA86), ROUND(X86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="F86" s="54">
+      <c r="F86" s="41">
         <f>IF(SUM($V86:$AA86), ROUND(Y86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="G86" s="54">
+      <c r="G86" s="41">
         <f>IF(SUM($V86:$AA86), ROUND(Z86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="H86" s="54">
+      <c r="H86" s="41">
         <f>IF(SUM($V86:$AA86), ROUND(AA86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
@@ -12747,27 +12755,27 @@
         <v>75</v>
       </c>
       <c r="B87" s="26" t="n"/>
-      <c r="C87" s="54">
+      <c r="C87" s="41">
         <f>IF(SUM($V87:$AA87), ROUND(V87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="D87" s="54">
+      <c r="D87" s="41">
         <f>IF(SUM($V87:$AA87), ROUND(W87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="E87" s="54">
+      <c r="E87" s="41">
         <f>IF(SUM($V87:$AA87), ROUND(X87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="F87" s="54">
+      <c r="F87" s="41">
         <f>IF(SUM($V87:$AA87), ROUND(Y87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="G87" s="54">
+      <c r="G87" s="41">
         <f>IF(SUM($V87:$AA87), ROUND(Z87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="H87" s="54">
+      <c r="H87" s="41">
         <f>IF(SUM($V87:$AA87), ROUND(AA87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
@@ -12827,27 +12835,27 @@
         <v>76</v>
       </c>
       <c r="B88" s="26" t="n"/>
-      <c r="C88" s="54">
+      <c r="C88" s="41">
         <f>IF(SUM($V88:$AA88), ROUND(V88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="D88" s="54">
+      <c r="D88" s="41">
         <f>IF(SUM($V88:$AA88), ROUND(W88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="E88" s="54">
+      <c r="E88" s="41">
         <f>IF(SUM($V88:$AA88), ROUND(X88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="F88" s="54">
+      <c r="F88" s="41">
         <f>IF(SUM($V88:$AA88), ROUND(Y88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="G88" s="54">
+      <c r="G88" s="41">
         <f>IF(SUM($V88:$AA88), ROUND(Z88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="H88" s="54">
+      <c r="H88" s="41">
         <f>IF(SUM($V88:$AA88), ROUND(AA88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
@@ -12907,27 +12915,27 @@
         <v>77</v>
       </c>
       <c r="B89" s="26" t="n"/>
-      <c r="C89" s="54">
+      <c r="C89" s="41">
         <f>IF(SUM($V89:$AA89), ROUND(V89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="D89" s="54">
+      <c r="D89" s="41">
         <f>IF(SUM($V89:$AA89), ROUND(W89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="E89" s="54">
+      <c r="E89" s="41">
         <f>IF(SUM($V89:$AA89), ROUND(X89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="F89" s="54">
+      <c r="F89" s="41">
         <f>IF(SUM($V89:$AA89), ROUND(Y89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="G89" s="54">
+      <c r="G89" s="41">
         <f>IF(SUM($V89:$AA89), ROUND(Z89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="H89" s="54">
+      <c r="H89" s="41">
         <f>IF(SUM($V89:$AA89), ROUND(AA89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
@@ -12987,27 +12995,27 @@
         <v>78</v>
       </c>
       <c r="B90" s="26" t="n"/>
-      <c r="C90" s="54">
+      <c r="C90" s="41">
         <f>IF(SUM($V90:$AA90), ROUND(V90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="D90" s="54">
+      <c r="D90" s="41">
         <f>IF(SUM($V90:$AA90), ROUND(W90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="E90" s="54">
+      <c r="E90" s="41">
         <f>IF(SUM($V90:$AA90), ROUND(X90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="F90" s="54">
+      <c r="F90" s="41">
         <f>IF(SUM($V90:$AA90), ROUND(Y90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="G90" s="54">
+      <c r="G90" s="41">
         <f>IF(SUM($V90:$AA90), ROUND(Z90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="H90" s="54">
+      <c r="H90" s="41">
         <f>IF(SUM($V90:$AA90), ROUND(AA90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
@@ -13067,27 +13075,27 @@
         <v>79</v>
       </c>
       <c r="B91" s="26" t="n"/>
-      <c r="C91" s="54">
+      <c r="C91" s="41">
         <f>IF(SUM($V91:$AA91), ROUND(V91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="D91" s="54">
+      <c r="D91" s="41">
         <f>IF(SUM($V91:$AA91), ROUND(W91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="E91" s="54">
+      <c r="E91" s="41">
         <f>IF(SUM($V91:$AA91), ROUND(X91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="F91" s="54">
+      <c r="F91" s="41">
         <f>IF(SUM($V91:$AA91), ROUND(Y91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="G91" s="54">
+      <c r="G91" s="41">
         <f>IF(SUM($V91:$AA91), ROUND(Z91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="H91" s="54">
+      <c r="H91" s="41">
         <f>IF(SUM($V91:$AA91), ROUND(AA91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
@@ -13147,27 +13155,27 @@
         <v>80</v>
       </c>
       <c r="B92" s="26" t="n"/>
-      <c r="C92" s="54">
+      <c r="C92" s="41">
         <f>IF(SUM($V92:$AA92), ROUND(V92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="D92" s="54">
+      <c r="D92" s="41">
         <f>IF(SUM($V92:$AA92), ROUND(W92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="E92" s="54">
+      <c r="E92" s="41">
         <f>IF(SUM($V92:$AA92), ROUND(X92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="F92" s="54">
+      <c r="F92" s="41">
         <f>IF(SUM($V92:$AA92), ROUND(Y92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="G92" s="54">
+      <c r="G92" s="41">
         <f>IF(SUM($V92:$AA92), ROUND(Z92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="H92" s="54">
+      <c r="H92" s="41">
         <f>IF(SUM($V92:$AA92), ROUND(AA92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
@@ -13227,27 +13235,27 @@
         <v>81</v>
       </c>
       <c r="B93" s="26" t="n"/>
-      <c r="C93" s="54">
+      <c r="C93" s="41">
         <f>IF(SUM($V93:$AA93), ROUND(V93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="D93" s="54">
+      <c r="D93" s="41">
         <f>IF(SUM($V93:$AA93), ROUND(W93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="E93" s="54">
+      <c r="E93" s="41">
         <f>IF(SUM($V93:$AA93), ROUND(X93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="F93" s="54">
+      <c r="F93" s="41">
         <f>IF(SUM($V93:$AA93), ROUND(Y93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="G93" s="54">
+      <c r="G93" s="41">
         <f>IF(SUM($V93:$AA93), ROUND(Z93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="H93" s="54">
+      <c r="H93" s="41">
         <f>IF(SUM($V93:$AA93), ROUND(AA93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
@@ -13307,27 +13315,27 @@
         <v>82</v>
       </c>
       <c r="B94" s="26" t="n"/>
-      <c r="C94" s="54">
+      <c r="C94" s="41">
         <f>IF(SUM($V94:$AA94), ROUND(V94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="D94" s="54">
+      <c r="D94" s="41">
         <f>IF(SUM($V94:$AA94), ROUND(W94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="E94" s="54">
+      <c r="E94" s="41">
         <f>IF(SUM($V94:$AA94), ROUND(X94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="F94" s="54">
+      <c r="F94" s="41">
         <f>IF(SUM($V94:$AA94), ROUND(Y94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="G94" s="54">
+      <c r="G94" s="41">
         <f>IF(SUM($V94:$AA94), ROUND(Z94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="H94" s="54">
+      <c r="H94" s="41">
         <f>IF(SUM($V94:$AA94), ROUND(AA94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
@@ -13387,27 +13395,27 @@
         <v>83</v>
       </c>
       <c r="B95" s="26" t="n"/>
-      <c r="C95" s="54">
+      <c r="C95" s="41">
         <f>IF(SUM($V95:$AA95), ROUND(V95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="D95" s="54">
+      <c r="D95" s="41">
         <f>IF(SUM($V95:$AA95), ROUND(W95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="E95" s="54">
+      <c r="E95" s="41">
         <f>IF(SUM($V95:$AA95), ROUND(X95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="F95" s="54">
+      <c r="F95" s="41">
         <f>IF(SUM($V95:$AA95), ROUND(Y95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="G95" s="54">
+      <c r="G95" s="41">
         <f>IF(SUM($V95:$AA95), ROUND(Z95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="H95" s="54">
+      <c r="H95" s="41">
         <f>IF(SUM($V95:$AA95), ROUND(AA95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
@@ -13467,27 +13475,27 @@
         <v>84</v>
       </c>
       <c r="B96" s="26" t="n"/>
-      <c r="C96" s="54">
+      <c r="C96" s="41">
         <f>IF(SUM($V96:$AA96), ROUND(V96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="D96" s="54">
+      <c r="D96" s="41">
         <f>IF(SUM($V96:$AA96), ROUND(W96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="E96" s="54">
+      <c r="E96" s="41">
         <f>IF(SUM($V96:$AA96), ROUND(X96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="F96" s="54">
+      <c r="F96" s="41">
         <f>IF(SUM($V96:$AA96), ROUND(Y96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="G96" s="54">
+      <c r="G96" s="41">
         <f>IF(SUM($V96:$AA96), ROUND(Z96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="H96" s="54">
+      <c r="H96" s="41">
         <f>IF(SUM($V96:$AA96), ROUND(AA96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
@@ -13547,27 +13555,27 @@
         <v>85</v>
       </c>
       <c r="B97" s="26" t="n"/>
-      <c r="C97" s="54">
+      <c r="C97" s="41">
         <f>IF(SUM($V97:$AA97), ROUND(V97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="D97" s="54">
+      <c r="D97" s="41">
         <f>IF(SUM($V97:$AA97), ROUND(W97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="E97" s="54">
+      <c r="E97" s="41">
         <f>IF(SUM($V97:$AA97), ROUND(X97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="F97" s="54">
+      <c r="F97" s="41">
         <f>IF(SUM($V97:$AA97), ROUND(Y97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="G97" s="54">
+      <c r="G97" s="41">
         <f>IF(SUM($V97:$AA97), ROUND(Z97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="H97" s="54">
+      <c r="H97" s="41">
         <f>IF(SUM($V97:$AA97), ROUND(AA97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
@@ -13627,27 +13635,27 @@
         <v>86</v>
       </c>
       <c r="B98" s="26" t="n"/>
-      <c r="C98" s="54">
+      <c r="C98" s="41">
         <f>IF(SUM($V98:$AA98), ROUND(V98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="D98" s="54">
+      <c r="D98" s="41">
         <f>IF(SUM($V98:$AA98), ROUND(W98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="E98" s="54">
+      <c r="E98" s="41">
         <f>IF(SUM($V98:$AA98), ROUND(X98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="F98" s="54">
+      <c r="F98" s="41">
         <f>IF(SUM($V98:$AA98), ROUND(Y98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="G98" s="54">
+      <c r="G98" s="41">
         <f>IF(SUM($V98:$AA98), ROUND(Z98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="H98" s="54">
+      <c r="H98" s="41">
         <f>IF(SUM($V98:$AA98), ROUND(AA98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
@@ -13707,27 +13715,27 @@
         <v>87</v>
       </c>
       <c r="B99" s="26" t="n"/>
-      <c r="C99" s="54">
+      <c r="C99" s="41">
         <f>IF(SUM($V99:$AA99), ROUND(V99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="D99" s="54">
+      <c r="D99" s="41">
         <f>IF(SUM($V99:$AA99), ROUND(W99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="E99" s="54">
+      <c r="E99" s="41">
         <f>IF(SUM($V99:$AA99), ROUND(X99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="F99" s="54">
+      <c r="F99" s="41">
         <f>IF(SUM($V99:$AA99), ROUND(Y99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="G99" s="54">
+      <c r="G99" s="41">
         <f>IF(SUM($V99:$AA99), ROUND(Z99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="H99" s="54">
+      <c r="H99" s="41">
         <f>IF(SUM($V99:$AA99), ROUND(AA99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
@@ -13787,27 +13795,27 @@
         <v>88</v>
       </c>
       <c r="B100" s="26" t="n"/>
-      <c r="C100" s="54">
+      <c r="C100" s="41">
         <f>IF(SUM($V100:$AA100), ROUND(V100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="D100" s="54">
+      <c r="D100" s="41">
         <f>IF(SUM($V100:$AA100), ROUND(W100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="E100" s="54">
+      <c r="E100" s="41">
         <f>IF(SUM($V100:$AA100), ROUND(X100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="F100" s="54">
+      <c r="F100" s="41">
         <f>IF(SUM($V100:$AA100), ROUND(Y100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="G100" s="54">
+      <c r="G100" s="41">
         <f>IF(SUM($V100:$AA100), ROUND(Z100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="H100" s="54">
+      <c r="H100" s="41">
         <f>IF(SUM($V100:$AA100), ROUND(AA100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
@@ -13867,27 +13875,27 @@
         <v>89</v>
       </c>
       <c r="B101" s="26" t="n"/>
-      <c r="C101" s="54">
+      <c r="C101" s="41">
         <f>IF(SUM($V101:$AA101), ROUND(V101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="D101" s="54">
+      <c r="D101" s="41">
         <f>IF(SUM($V101:$AA101), ROUND(W101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="E101" s="54">
+      <c r="E101" s="41">
         <f>IF(SUM($V101:$AA101), ROUND(X101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="F101" s="54">
+      <c r="F101" s="41">
         <f>IF(SUM($V101:$AA101), ROUND(Y101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="G101" s="54">
+      <c r="G101" s="41">
         <f>IF(SUM($V101:$AA101), ROUND(Z101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="H101" s="54">
+      <c r="H101" s="41">
         <f>IF(SUM($V101:$AA101), ROUND(AA101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
@@ -13947,27 +13955,27 @@
         <v>90</v>
       </c>
       <c r="B102" s="26" t="n"/>
-      <c r="C102" s="54">
+      <c r="C102" s="41">
         <f>IF(SUM($V102:$AA102), ROUND(V102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="D102" s="54">
+      <c r="D102" s="41">
         <f>IF(SUM($V102:$AA102), ROUND(W102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="E102" s="54">
+      <c r="E102" s="41">
         <f>IF(SUM($V102:$AA102), ROUND(X102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="F102" s="54">
+      <c r="F102" s="41">
         <f>IF(SUM($V102:$AA102), ROUND(Y102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="G102" s="54">
+      <c r="G102" s="41">
         <f>IF(SUM($V102:$AA102), ROUND(Z102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="H102" s="54">
+      <c r="H102" s="41">
         <f>IF(SUM($V102:$AA102), ROUND(AA102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
@@ -14027,27 +14035,27 @@
         <v>91</v>
       </c>
       <c r="B103" s="26" t="n"/>
-      <c r="C103" s="54">
+      <c r="C103" s="41">
         <f>IF(SUM($V103:$AA103), ROUND(V103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="D103" s="54">
+      <c r="D103" s="41">
         <f>IF(SUM($V103:$AA103), ROUND(W103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="E103" s="54">
+      <c r="E103" s="41">
         <f>IF(SUM($V103:$AA103), ROUND(X103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="F103" s="54">
+      <c r="F103" s="41">
         <f>IF(SUM($V103:$AA103), ROUND(Y103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="G103" s="54">
+      <c r="G103" s="41">
         <f>IF(SUM($V103:$AA103), ROUND(Z103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="H103" s="54">
+      <c r="H103" s="41">
         <f>IF(SUM($V103:$AA103), ROUND(AA103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
@@ -14107,27 +14115,27 @@
         <v>92</v>
       </c>
       <c r="B104" s="26" t="n"/>
-      <c r="C104" s="54">
+      <c r="C104" s="41">
         <f>IF(SUM($V104:$AA104), ROUND(V104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="D104" s="54">
+      <c r="D104" s="41">
         <f>IF(SUM($V104:$AA104), ROUND(W104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="E104" s="54">
+      <c r="E104" s="41">
         <f>IF(SUM($V104:$AA104), ROUND(X104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="F104" s="54">
+      <c r="F104" s="41">
         <f>IF(SUM($V104:$AA104), ROUND(Y104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="G104" s="54">
+      <c r="G104" s="41">
         <f>IF(SUM($V104:$AA104), ROUND(Z104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="H104" s="54">
+      <c r="H104" s="41">
         <f>IF(SUM($V104:$AA104), ROUND(AA104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
@@ -14187,27 +14195,27 @@
         <v>93</v>
       </c>
       <c r="B105" s="26" t="n"/>
-      <c r="C105" s="54">
+      <c r="C105" s="41">
         <f>IF(SUM($V105:$AA105), ROUND(V105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="D105" s="54">
+      <c r="D105" s="41">
         <f>IF(SUM($V105:$AA105), ROUND(W105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="E105" s="54">
+      <c r="E105" s="41">
         <f>IF(SUM($V105:$AA105), ROUND(X105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="F105" s="54">
+      <c r="F105" s="41">
         <f>IF(SUM($V105:$AA105), ROUND(Y105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="G105" s="54">
+      <c r="G105" s="41">
         <f>IF(SUM($V105:$AA105), ROUND(Z105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="H105" s="54">
+      <c r="H105" s="41">
         <f>IF(SUM($V105:$AA105), ROUND(AA105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
@@ -14267,27 +14275,27 @@
         <v>94</v>
       </c>
       <c r="B106" s="26" t="n"/>
-      <c r="C106" s="54">
+      <c r="C106" s="41">
         <f>IF(SUM($V106:$AA106), ROUND(V106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="D106" s="54">
+      <c r="D106" s="41">
         <f>IF(SUM($V106:$AA106), ROUND(W106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="E106" s="54">
+      <c r="E106" s="41">
         <f>IF(SUM($V106:$AA106), ROUND(X106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="F106" s="54">
+      <c r="F106" s="41">
         <f>IF(SUM($V106:$AA106), ROUND(Y106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="G106" s="54">
+      <c r="G106" s="41">
         <f>IF(SUM($V106:$AA106), ROUND(Z106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="H106" s="54">
+      <c r="H106" s="41">
         <f>IF(SUM($V106:$AA106), ROUND(AA106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
@@ -14347,27 +14355,27 @@
         <v>95</v>
       </c>
       <c r="B107" s="26" t="n"/>
-      <c r="C107" s="54">
+      <c r="C107" s="41">
         <f>IF(SUM($V107:$AA107), ROUND(V107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="D107" s="54">
+      <c r="D107" s="41">
         <f>IF(SUM($V107:$AA107), ROUND(W107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="E107" s="54">
+      <c r="E107" s="41">
         <f>IF(SUM($V107:$AA107), ROUND(X107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="F107" s="54">
+      <c r="F107" s="41">
         <f>IF(SUM($V107:$AA107), ROUND(Y107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="G107" s="54">
+      <c r="G107" s="41">
         <f>IF(SUM($V107:$AA107), ROUND(Z107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="H107" s="54">
+      <c r="H107" s="41">
         <f>IF(SUM($V107:$AA107), ROUND(AA107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
@@ -14427,27 +14435,27 @@
         <v>96</v>
       </c>
       <c r="B108" s="26" t="n"/>
-      <c r="C108" s="54">
+      <c r="C108" s="41">
         <f>IF(SUM($V108:$AA108), ROUND(V108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="D108" s="54">
+      <c r="D108" s="41">
         <f>IF(SUM($V108:$AA108), ROUND(W108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="E108" s="54">
+      <c r="E108" s="41">
         <f>IF(SUM($V108:$AA108), ROUND(X108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="F108" s="54">
+      <c r="F108" s="41">
         <f>IF(SUM($V108:$AA108), ROUND(Y108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="G108" s="54">
+      <c r="G108" s="41">
         <f>IF(SUM($V108:$AA108), ROUND(Z108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="H108" s="54">
+      <c r="H108" s="41">
         <f>IF(SUM($V108:$AA108), ROUND(AA108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
@@ -14507,27 +14515,27 @@
         <v>97</v>
       </c>
       <c r="B109" s="26" t="n"/>
-      <c r="C109" s="54">
+      <c r="C109" s="41">
         <f>IF(SUM($V109:$AA109), ROUND(V109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="D109" s="54">
+      <c r="D109" s="41">
         <f>IF(SUM($V109:$AA109), ROUND(W109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="E109" s="54">
+      <c r="E109" s="41">
         <f>IF(SUM($V109:$AA109), ROUND(X109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="F109" s="54">
+      <c r="F109" s="41">
         <f>IF(SUM($V109:$AA109), ROUND(Y109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="G109" s="54">
+      <c r="G109" s="41">
         <f>IF(SUM($V109:$AA109), ROUND(Z109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="H109" s="54">
+      <c r="H109" s="41">
         <f>IF(SUM($V109:$AA109), ROUND(AA109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
@@ -14587,27 +14595,27 @@
         <v>98</v>
       </c>
       <c r="B110" s="26" t="n"/>
-      <c r="C110" s="54">
+      <c r="C110" s="41">
         <f>IF(SUM($V110:$AA110), ROUND(V110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="D110" s="54">
+      <c r="D110" s="41">
         <f>IF(SUM($V110:$AA110), ROUND(W110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="E110" s="54">
+      <c r="E110" s="41">
         <f>IF(SUM($V110:$AA110), ROUND(X110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="F110" s="54">
+      <c r="F110" s="41">
         <f>IF(SUM($V110:$AA110), ROUND(Y110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="G110" s="54">
+      <c r="G110" s="41">
         <f>IF(SUM($V110:$AA110), ROUND(Z110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="H110" s="54">
+      <c r="H110" s="41">
         <f>IF(SUM($V110:$AA110), ROUND(AA110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
@@ -14667,27 +14675,27 @@
         <v>99</v>
       </c>
       <c r="B111" s="26" t="n"/>
-      <c r="C111" s="54">
+      <c r="C111" s="41">
         <f>IF(SUM($V111:$AA111), ROUND(V111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="D111" s="54">
+      <c r="D111" s="41">
         <f>IF(SUM($V111:$AA111), ROUND(W111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="E111" s="54">
+      <c r="E111" s="41">
         <f>IF(SUM($V111:$AA111), ROUND(X111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="F111" s="54">
+      <c r="F111" s="41">
         <f>IF(SUM($V111:$AA111), ROUND(Y111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="G111" s="54">
+      <c r="G111" s="41">
         <f>IF(SUM($V111:$AA111), ROUND(Z111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="H111" s="54">
+      <c r="H111" s="41">
         <f>IF(SUM($V111:$AA111), ROUND(AA111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
@@ -14747,27 +14755,27 @@
         <v>100</v>
       </c>
       <c r="B112" s="28" t="n"/>
-      <c r="C112" s="55">
+      <c r="C112" s="42">
         <f>IF(SUM($V112:$AA112), ROUND(V112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="D112" s="55">
+      <c r="D112" s="42">
         <f>IF(SUM($V112:$AA112), ROUND(W112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="E112" s="55">
+      <c r="E112" s="42">
         <f>IF(SUM($V112:$AA112), ROUND(X112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="F112" s="55">
+      <c r="F112" s="42">
         <f>IF(SUM($V112:$AA112), ROUND(Y112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="G112" s="55">
+      <c r="G112" s="42">
         <f>IF(SUM($V112:$AA112), ROUND(Z112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="H112" s="55">
+      <c r="H112" s="42">
         <f>IF(SUM($V112:$AA112), ROUND(AA112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
@@ -15202,16 +15210,13 @@
     <row r="123" ht="35.1" customHeight="1"/>
     <row r="124" ht="33.95" customHeight="1"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="V11:AA11"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="O11:T11"/>
     <mergeCell ref="A11:A12"/>
